--- a/research/traditional_assets/database/data/iceland/iceland_food_wholesalers.xlsx
+++ b/research/traditional_assets/database/data/iceland/iceland_food_wholesalers.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07239088921648647</v>
+        <v>0.07228210743805349</v>
       </c>
       <c r="C2">
-        <v>231.8322387747587</v>
+        <v>229.9242520490215</v>
       </c>
       <c r="D2">
-        <v>218.2322387747587</v>
+        <v>218.7532520490215</v>
       </c>
       <c r="E2">
-        <v>-130.9</v>
+        <v>-128.471</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.429</v>
       </c>
       <c r="G2">
         <v>13.6</v>
@@ -1439,28 +1439,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1221787</v>
       </c>
       <c r="N2">
-        <v>22.72666666666667</v>
+        <v>22.60448796666667</v>
       </c>
       <c r="O2">
-        <v>4.545333333333334</v>
+        <v>4.520897593333333</v>
       </c>
       <c r="P2">
-        <v>18.18133333333333</v>
+        <v>18.08359037333333</v>
       </c>
       <c r="Q2">
-        <v>22.92133333333334</v>
+        <v>22.82359037333333</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07239088921648647</v>
+        <v>0.07260576508894293</v>
       </c>
       <c r="T2">
-        <v>0.5044193424952811</v>
+        <v>0.5084954583942328</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>186.0116916178243</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07228210743805349</v>
+        <v>0.07217332565962051</v>
       </c>
       <c r="C3">
-        <v>229.9242520490215</v>
+        <v>228.0187590378949</v>
       </c>
       <c r="D3">
-        <v>218.7532520490215</v>
+        <v>219.2767590378949</v>
       </c>
       <c r="E3">
-        <v>-128.471</v>
+        <v>-126.042</v>
       </c>
       <c r="F3">
-        <v>2.429</v>
+        <v>4.858000000000001</v>
       </c>
       <c r="G3">
         <v>13.6</v>
@@ -1521,28 +1521,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M3">
-        <v>0.1221787</v>
+        <v>0.2443574</v>
       </c>
       <c r="N3">
-        <v>22.60448796666667</v>
+        <v>22.48230926666667</v>
       </c>
       <c r="O3">
-        <v>4.520897593333333</v>
+        <v>4.496461853333334</v>
       </c>
       <c r="P3">
-        <v>18.08359037333333</v>
+        <v>17.98584741333334</v>
       </c>
       <c r="Q3">
-        <v>22.82359037333333</v>
+        <v>22.72584741333333</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07260576508894293</v>
+        <v>0.07282502618328623</v>
       </c>
       <c r="T3">
-        <v>0.5084954583942328</v>
+        <v>0.5126547603319387</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>186.0116916178243</v>
+        <v>93.00584580891214</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07217332565962051</v>
+        <v>0.07206454388118755</v>
       </c>
       <c r="C4">
-        <v>228.0187590378949</v>
+        <v>226.1157776877458</v>
       </c>
       <c r="D4">
-        <v>219.2767590378949</v>
+        <v>219.8027776877458</v>
       </c>
       <c r="E4">
-        <v>-126.042</v>
+        <v>-123.613</v>
       </c>
       <c r="F4">
-        <v>4.858000000000001</v>
+        <v>7.287</v>
       </c>
       <c r="G4">
         <v>13.6</v>
@@ -1603,28 +1603,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M4">
-        <v>0.2443574</v>
+        <v>0.3665361</v>
       </c>
       <c r="N4">
-        <v>22.48230926666667</v>
+        <v>22.36013056666667</v>
       </c>
       <c r="O4">
-        <v>4.496461853333334</v>
+        <v>4.472026113333333</v>
       </c>
       <c r="P4">
-        <v>17.98584741333334</v>
+        <v>17.88810445333333</v>
       </c>
       <c r="Q4">
-        <v>22.72584741333333</v>
+        <v>22.62810445333334</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07282502618328623</v>
+        <v>0.07304880812493561</v>
       </c>
       <c r="T4">
-        <v>0.5126547603319387</v>
+        <v>0.5168998210724839</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>93.00584580891214</v>
+        <v>62.00389720594143</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07206454388118755</v>
+        <v>0.07195576210275458</v>
       </c>
       <c r="C5">
-        <v>226.1157776877458</v>
+        <v>224.21532611756</v>
       </c>
       <c r="D5">
-        <v>219.8027776877458</v>
+        <v>220.33132611756</v>
       </c>
       <c r="E5">
-        <v>-123.613</v>
+        <v>-121.184</v>
       </c>
       <c r="F5">
-        <v>7.287</v>
+        <v>9.716000000000001</v>
       </c>
       <c r="G5">
         <v>13.6</v>
@@ -1685,28 +1685,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M5">
-        <v>0.3665361</v>
+        <v>0.4887148</v>
       </c>
       <c r="N5">
-        <v>22.36013056666667</v>
+        <v>22.23795186666667</v>
       </c>
       <c r="O5">
-        <v>4.472026113333333</v>
+        <v>4.447590373333333</v>
       </c>
       <c r="P5">
-        <v>17.88810445333333</v>
+        <v>17.79036149333333</v>
       </c>
       <c r="Q5">
-        <v>22.62810445333334</v>
+        <v>22.53036149333333</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07304880812493561</v>
+        <v>0.07327725219036935</v>
       </c>
       <c r="T5">
-        <v>0.5168998210724839</v>
+        <v>0.5212333205784572</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>62.00389720594143</v>
+        <v>46.50292290445607</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07195576210275458</v>
+        <v>0.0718469803243216</v>
       </c>
       <c r="C6">
-        <v>224.21532611756</v>
+        <v>222.3174226210224</v>
       </c>
       <c r="D6">
-        <v>220.33132611756</v>
+        <v>220.8624226210224</v>
       </c>
       <c r="E6">
-        <v>-121.184</v>
+        <v>-118.755</v>
       </c>
       <c r="F6">
-        <v>9.716000000000001</v>
+        <v>12.145</v>
       </c>
       <c r="G6">
         <v>13.6</v>
@@ -1767,28 +1767,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M6">
-        <v>0.4887148</v>
+        <v>0.6108935000000001</v>
       </c>
       <c r="N6">
-        <v>22.23795186666667</v>
+        <v>22.11577316666667</v>
       </c>
       <c r="O6">
-        <v>4.447590373333333</v>
+        <v>4.423154633333334</v>
       </c>
       <c r="P6">
-        <v>17.79036149333333</v>
+        <v>17.69261853333333</v>
       </c>
       <c r="Q6">
-        <v>22.53036149333333</v>
+        <v>22.43261853333333</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07327725219036935</v>
+        <v>0.07351050560454905</v>
       </c>
       <c r="T6">
-        <v>0.5212333205784572</v>
+        <v>0.5256580516529771</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>46.50292290445607</v>
+        <v>37.20233832356485</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0718469803243216</v>
+        <v>0.07173819854588862</v>
       </c>
       <c r="C7">
-        <v>222.3174226210224</v>
+        <v>220.4220856686281</v>
       </c>
       <c r="D7">
-        <v>220.8624226210224</v>
+        <v>221.3960856686281</v>
       </c>
       <c r="E7">
-        <v>-118.755</v>
+        <v>-116.326</v>
       </c>
       <c r="F7">
-        <v>12.145</v>
+        <v>14.574</v>
       </c>
       <c r="G7">
         <v>13.6</v>
@@ -1849,28 +1849,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M7">
-        <v>0.6108935000000001</v>
+        <v>0.7330722000000001</v>
       </c>
       <c r="N7">
-        <v>22.11577316666667</v>
+        <v>21.99359446666667</v>
       </c>
       <c r="O7">
-        <v>4.423154633333334</v>
+        <v>4.398718893333334</v>
       </c>
       <c r="P7">
-        <v>17.69261853333333</v>
+        <v>17.59487557333333</v>
       </c>
       <c r="Q7">
-        <v>22.43261853333333</v>
+        <v>22.33487557333333</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07351050560454905</v>
+        <v>0.07374872185732832</v>
       </c>
       <c r="T7">
-        <v>0.5256580516529771</v>
+        <v>0.5301769259418486</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>37.20233832356485</v>
+        <v>31.00194860297071</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07173819854588862</v>
+        <v>0.07162941676745564</v>
       </c>
       <c r="C8">
-        <v>220.4220856686281</v>
+        <v>218.5293339098229</v>
       </c>
       <c r="D8">
-        <v>221.3960856686281</v>
+        <v>221.9323339098229</v>
       </c>
       <c r="E8">
-        <v>-116.326</v>
+        <v>-113.897</v>
       </c>
       <c r="F8">
-        <v>14.574</v>
+        <v>17.003</v>
       </c>
       <c r="G8">
         <v>13.6</v>
@@ -1931,28 +1931,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M8">
-        <v>0.7330722</v>
+        <v>0.8552508999999999</v>
       </c>
       <c r="N8">
-        <v>21.99359446666667</v>
+        <v>21.87141576666667</v>
       </c>
       <c r="O8">
-        <v>4.398718893333334</v>
+        <v>4.374283153333333</v>
       </c>
       <c r="P8">
-        <v>17.59487557333333</v>
+        <v>17.49713261333333</v>
       </c>
       <c r="Q8">
-        <v>22.33487557333333</v>
+        <v>22.23713261333333</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07374872185732832</v>
+        <v>0.07399206104027489</v>
       </c>
       <c r="T8">
-        <v>0.5301769259418486</v>
+        <v>0.534792980322954</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>31.00194860297072</v>
+        <v>26.57309880254633</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07162941676745564</v>
+        <v>0.0715206349890227</v>
       </c>
       <c r="C9">
-        <v>218.5293339098229</v>
+        <v>216.6391861751763</v>
       </c>
       <c r="D9">
-        <v>221.9323339098229</v>
+        <v>222.4711861751763</v>
       </c>
       <c r="E9">
-        <v>-113.897</v>
+        <v>-111.468</v>
       </c>
       <c r="F9">
-        <v>17.003</v>
+        <v>19.432</v>
       </c>
       <c r="G9">
         <v>13.6</v>
@@ -2013,28 +2013,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M9">
-        <v>0.8552509000000001</v>
+        <v>0.9774296</v>
       </c>
       <c r="N9">
-        <v>21.87141576666667</v>
+        <v>21.74923706666667</v>
       </c>
       <c r="O9">
-        <v>4.374283153333333</v>
+        <v>4.349847413333333</v>
       </c>
       <c r="P9">
-        <v>17.49713261333333</v>
+        <v>17.39938965333333</v>
       </c>
       <c r="Q9">
-        <v>22.23713261333333</v>
+        <v>22.13938965333333</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07399206104027489</v>
+        <v>0.07424069020545944</v>
       </c>
       <c r="T9">
-        <v>0.534792980322954</v>
+        <v>0.5395093837123441</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>26.57309880254632</v>
+        <v>23.25146145222803</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0715206349890227</v>
+        <v>0.07141185321058971</v>
       </c>
       <c r="C10">
-        <v>216.6391861751763</v>
+        <v>214.7516614785862</v>
       </c>
       <c r="D10">
-        <v>222.4711861751763</v>
+        <v>223.0126614785862</v>
       </c>
       <c r="E10">
-        <v>-111.468</v>
+        <v>-109.039</v>
       </c>
       <c r="F10">
-        <v>19.432</v>
+        <v>21.861</v>
       </c>
       <c r="G10">
         <v>13.6</v>
@@ -2095,28 +2095,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M10">
-        <v>0.9774296</v>
+        <v>1.0996083</v>
       </c>
       <c r="N10">
-        <v>21.74923706666667</v>
+        <v>21.62705836666667</v>
       </c>
       <c r="O10">
-        <v>4.349847413333333</v>
+        <v>4.325411673333334</v>
       </c>
       <c r="P10">
-        <v>17.39938965333333</v>
+        <v>17.30164669333333</v>
       </c>
       <c r="Q10">
-        <v>22.13938965333333</v>
+        <v>22.04164669333333</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07424069020545944</v>
+        <v>0.07449478374790078</v>
       </c>
       <c r="T10">
-        <v>0.5395093837123441</v>
+        <v>0.5443294443190835</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.25146145222803</v>
+        <v>20.66796573531381</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07141185321058971</v>
+        <v>0.07130307143215672</v>
       </c>
       <c r="C11">
-        <v>214.7516614785862</v>
+        <v>212.866779019514</v>
       </c>
       <c r="D11">
-        <v>223.0126614785862</v>
+        <v>223.556779019514</v>
       </c>
       <c r="E11">
-        <v>-109.039</v>
+        <v>-106.61</v>
       </c>
       <c r="F11">
-        <v>21.861</v>
+        <v>24.29</v>
       </c>
       <c r="G11">
         <v>13.6</v>
@@ -2177,28 +2177,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M11">
-        <v>1.0996083</v>
+        <v>1.221787</v>
       </c>
       <c r="N11">
-        <v>21.62705836666667</v>
+        <v>21.50487966666667</v>
       </c>
       <c r="O11">
-        <v>4.325411673333334</v>
+        <v>4.300975933333334</v>
       </c>
       <c r="P11">
-        <v>17.30164669333333</v>
+        <v>17.20390373333333</v>
       </c>
       <c r="Q11">
-        <v>22.04164669333333</v>
+        <v>21.94390373333334</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07449478374790078</v>
+        <v>0.07475452381350747</v>
       </c>
       <c r="T11">
-        <v>0.5443294443190835</v>
+        <v>0.5492566173837504</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>20.66796573531381</v>
+        <v>18.60116916178243</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07130307143215674</v>
+        <v>0.07119428965372375</v>
       </c>
       <c r="C12">
-        <v>212.8667790195139</v>
+        <v>210.9845581852548</v>
       </c>
       <c r="D12">
-        <v>223.5567790195139</v>
+        <v>224.1035581852548</v>
       </c>
       <c r="E12">
-        <v>-106.61</v>
+        <v>-104.181</v>
       </c>
       <c r="F12">
-        <v>24.29</v>
+        <v>26.719</v>
       </c>
       <c r="G12">
         <v>13.6</v>
@@ -2259,28 +2259,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M12">
-        <v>1.221787</v>
+        <v>1.3439657</v>
       </c>
       <c r="N12">
-        <v>21.50487966666667</v>
+        <v>21.38270096666667</v>
       </c>
       <c r="O12">
-        <v>4.300975933333334</v>
+        <v>4.276540193333334</v>
       </c>
       <c r="P12">
-        <v>17.20390373333333</v>
+        <v>17.10616077333334</v>
       </c>
       <c r="Q12">
-        <v>21.94390373333334</v>
+        <v>21.84616077333334</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07475452381350749</v>
+        <v>0.07502010073452108</v>
       </c>
       <c r="T12">
-        <v>0.5492566173837505</v>
+        <v>0.5542945134386347</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.60116916178243</v>
+        <v>16.91015378343857</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07119428965372375</v>
+        <v>0.07108550787529079</v>
       </c>
       <c r="C13">
-        <v>210.9845581852548</v>
+        <v>209.1050185532402</v>
       </c>
       <c r="D13">
-        <v>224.1035581852548</v>
+        <v>224.6530185532402</v>
       </c>
       <c r="E13">
-        <v>-104.181</v>
+        <v>-101.752</v>
       </c>
       <c r="F13">
-        <v>26.719</v>
+        <v>29.148</v>
       </c>
       <c r="G13">
         <v>13.6</v>
@@ -2341,28 +2341,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M13">
-        <v>1.3439657</v>
+        <v>1.4661444</v>
       </c>
       <c r="N13">
-        <v>21.38270096666667</v>
+        <v>21.26052226666667</v>
       </c>
       <c r="O13">
-        <v>4.276540193333334</v>
+        <v>4.252104453333334</v>
       </c>
       <c r="P13">
-        <v>17.10616077333334</v>
+        <v>17.00841781333333</v>
       </c>
       <c r="Q13">
-        <v>21.84616077333334</v>
+        <v>21.74841781333333</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07502010073452108</v>
+        <v>0.07529171349464862</v>
       </c>
       <c r="T13">
-        <v>0.5542945134386347</v>
+        <v>0.55944690713113</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.91015378343857</v>
+        <v>15.50097430148536</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07108550787529079</v>
+        <v>0.07097672609685782</v>
       </c>
       <c r="C14">
-        <v>209.1050185532402</v>
+        <v>207.2281798933746</v>
       </c>
       <c r="D14">
-        <v>224.6530185532402</v>
+        <v>225.2051798933746</v>
       </c>
       <c r="E14">
-        <v>-101.752</v>
+        <v>-99.32300000000001</v>
       </c>
       <c r="F14">
-        <v>29.148</v>
+        <v>31.577</v>
       </c>
       <c r="G14">
         <v>13.6</v>
@@ -2423,28 +2423,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M14">
-        <v>1.4661444</v>
+        <v>1.5883231</v>
       </c>
       <c r="N14">
-        <v>21.26052226666667</v>
+        <v>21.13834356666667</v>
       </c>
       <c r="O14">
-        <v>4.252104453333334</v>
+        <v>4.227668713333333</v>
       </c>
       <c r="P14">
-        <v>17.00841781333333</v>
+        <v>16.91067485333333</v>
       </c>
       <c r="Q14">
-        <v>21.74841781333333</v>
+        <v>21.65067485333334</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07529171349464862</v>
+        <v>0.07556957022627335</v>
       </c>
       <c r="T14">
-        <v>0.55944690713113</v>
+        <v>0.5647177466556365</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.50097430148536</v>
+        <v>14.30859166290956</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07097672609685782</v>
+        <v>0.07086794431842484</v>
       </c>
       <c r="C15">
-        <v>207.2281798933746</v>
+        <v>205.3540621704061</v>
       </c>
       <c r="D15">
-        <v>225.2051798933746</v>
+        <v>225.7600621704061</v>
       </c>
       <c r="E15">
-        <v>-99.32300000000001</v>
+        <v>-96.89400000000001</v>
       </c>
       <c r="F15">
-        <v>31.577</v>
+        <v>34.00600000000001</v>
       </c>
       <c r="G15">
         <v>13.6</v>
@@ -2505,28 +2505,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M15">
-        <v>1.5883231</v>
+        <v>1.7105018</v>
       </c>
       <c r="N15">
-        <v>21.13834356666667</v>
+        <v>21.01616486666667</v>
       </c>
       <c r="O15">
-        <v>4.227668713333333</v>
+        <v>4.203232973333334</v>
       </c>
       <c r="P15">
-        <v>16.91067485333333</v>
+        <v>16.81293189333334</v>
       </c>
       <c r="Q15">
-        <v>21.65067485333334</v>
+        <v>21.55293189333334</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07556957022627335</v>
+        <v>0.07585388874235446</v>
       </c>
       <c r="T15">
-        <v>0.5647177466556365</v>
+        <v>0.5701111638435038</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.30859166290956</v>
+        <v>13.28654940127316</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07086794431842484</v>
+        <v>0.07093916253999187</v>
       </c>
       <c r="C16">
-        <v>205.3540621704061</v>
+        <v>202.5614783286588</v>
       </c>
       <c r="D16">
-        <v>225.7600621704061</v>
+        <v>225.3964783286588</v>
       </c>
       <c r="E16">
-        <v>-96.89400000000001</v>
+        <v>-94.465</v>
       </c>
       <c r="F16">
-        <v>34.00600000000001</v>
+        <v>36.43500000000001</v>
       </c>
       <c r="G16">
         <v>13.6</v>
@@ -2587,45 +2587,45 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M16">
-        <v>1.7105018</v>
+        <v>1.887333</v>
       </c>
       <c r="N16">
-        <v>21.01616486666667</v>
+        <v>20.83933366666666</v>
       </c>
       <c r="O16">
-        <v>4.203232973333334</v>
+        <v>4.167866733333333</v>
       </c>
       <c r="P16">
-        <v>16.81293189333334</v>
+        <v>16.67146693333333</v>
       </c>
       <c r="Q16">
-        <v>21.55293189333334</v>
+        <v>21.41146693333333</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07585388874235446</v>
+        <v>0.07614489710587279</v>
       </c>
       <c r="T16">
-        <v>0.5701111638435038</v>
+        <v>0.5756314849652031</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.28654940127316</v>
+        <v>12.04168351142414</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07093916253999187</v>
+        <v>0.0708423807615589</v>
       </c>
       <c r="C17">
-        <v>202.5614783286588</v>
+        <v>200.6268556984874</v>
       </c>
       <c r="D17">
-        <v>225.3964783286588</v>
+        <v>225.8908556984875</v>
       </c>
       <c r="E17">
-        <v>-94.465</v>
+        <v>-92.036</v>
       </c>
       <c r="F17">
-        <v>36.435</v>
+        <v>38.864</v>
       </c>
       <c r="G17">
         <v>13.6</v>
@@ -2669,28 +2669,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M17">
-        <v>1.887333</v>
+        <v>2.0131552</v>
       </c>
       <c r="N17">
-        <v>20.83933366666666</v>
+        <v>20.71351146666667</v>
       </c>
       <c r="O17">
-        <v>4.167866733333333</v>
+        <v>4.142702293333334</v>
       </c>
       <c r="P17">
-        <v>16.67146693333333</v>
+        <v>16.57080917333333</v>
       </c>
       <c r="Q17">
-        <v>21.41146693333333</v>
+        <v>21.31080917333333</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07614489710587279</v>
+        <v>0.07644283423995107</v>
       </c>
       <c r="T17">
-        <v>0.5756314849652031</v>
+        <v>0.5812832423040858</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.04168351142414</v>
+        <v>11.28907829196013</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0708423807615589</v>
+        <v>0.07074559898312592</v>
       </c>
       <c r="C18">
-        <v>200.6268556984874</v>
+        <v>198.6944065383083</v>
       </c>
       <c r="D18">
-        <v>225.8908556984875</v>
+        <v>226.3874065383083</v>
       </c>
       <c r="E18">
-        <v>-92.036</v>
+        <v>-89.607</v>
       </c>
       <c r="F18">
-        <v>38.864</v>
+        <v>41.29300000000001</v>
       </c>
       <c r="G18">
         <v>13.6</v>
@@ -2751,28 +2751,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M18">
-        <v>2.0131552</v>
+        <v>2.1389774</v>
       </c>
       <c r="N18">
-        <v>20.71351146666667</v>
+        <v>20.58768926666666</v>
       </c>
       <c r="O18">
-        <v>4.142702293333334</v>
+        <v>4.117537853333333</v>
       </c>
       <c r="P18">
-        <v>16.57080917333333</v>
+        <v>16.47015141333333</v>
       </c>
       <c r="Q18">
-        <v>21.31080917333333</v>
+        <v>21.21015141333334</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07644283423995107</v>
+        <v>0.07674795058207942</v>
       </c>
       <c r="T18">
-        <v>0.5812832423040858</v>
+        <v>0.587071186566797</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.28907829196013</v>
+        <v>10.6250148630213</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07074559898312592</v>
+        <v>0.07064881720469295</v>
       </c>
       <c r="C19">
-        <v>198.6944065383083</v>
+        <v>196.7641452127923</v>
       </c>
       <c r="D19">
-        <v>226.3874065383083</v>
+        <v>226.8861452127923</v>
       </c>
       <c r="E19">
-        <v>-89.607</v>
+        <v>-87.178</v>
       </c>
       <c r="F19">
-        <v>41.29300000000001</v>
+        <v>43.72200000000001</v>
       </c>
       <c r="G19">
         <v>13.6</v>
@@ -2833,28 +2833,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M19">
-        <v>2.1389774</v>
+        <v>2.2647996</v>
       </c>
       <c r="N19">
-        <v>20.58768926666666</v>
+        <v>20.46186706666667</v>
       </c>
       <c r="O19">
-        <v>4.117537853333333</v>
+        <v>4.092373413333333</v>
       </c>
       <c r="P19">
-        <v>16.47015141333333</v>
+        <v>16.36949365333333</v>
       </c>
       <c r="Q19">
-        <v>21.21015141333334</v>
+        <v>21.10949365333333</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07674795058207942</v>
+        <v>0.07706050878621092</v>
       </c>
       <c r="T19">
-        <v>0.587071186566797</v>
+        <v>0.5930003002017695</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.6250148630213</v>
+        <v>10.03473625952012</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07064881720469296</v>
+        <v>0.07081043542625998</v>
       </c>
       <c r="C20">
-        <v>196.7641452127922</v>
+        <v>193.5035141708653</v>
       </c>
       <c r="D20">
-        <v>226.8861452127922</v>
+        <v>226.0545141708653</v>
       </c>
       <c r="E20">
-        <v>-87.178</v>
+        <v>-84.749</v>
       </c>
       <c r="F20">
-        <v>43.722</v>
+        <v>46.151</v>
       </c>
       <c r="G20">
         <v>13.6</v>
@@ -2915,45 +2915,45 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M20">
-        <v>2.2647996</v>
+        <v>2.4690785</v>
       </c>
       <c r="N20">
-        <v>20.46186706666667</v>
+        <v>20.25758816666666</v>
       </c>
       <c r="O20">
-        <v>4.092373413333333</v>
+        <v>4.051517633333333</v>
       </c>
       <c r="P20">
-        <v>16.36949365333333</v>
+        <v>16.20607053333333</v>
       </c>
       <c r="Q20">
-        <v>21.10949365333333</v>
+        <v>20.94607053333333</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07706050878621092</v>
+        <v>0.07738078447686417</v>
       </c>
       <c r="T20">
-        <v>0.5930003002017694</v>
+        <v>0.5990758117042722</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.2</v>
       </c>
       <c r="W20">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>10.03473625952012</v>
+        <v>9.20451361374969</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07081043542625998</v>
+        <v>0.070727253647827</v>
       </c>
       <c r="C21">
-        <v>193.5035141708653</v>
+        <v>191.5017757630316</v>
       </c>
       <c r="D21">
-        <v>226.0545141708653</v>
+        <v>226.4817757630317</v>
       </c>
       <c r="E21">
-        <v>-84.749</v>
+        <v>-82.31999999999999</v>
       </c>
       <c r="F21">
-        <v>46.151</v>
+        <v>48.58000000000001</v>
       </c>
       <c r="G21">
         <v>13.6</v>
@@ -2997,28 +2997,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M21">
-        <v>2.4690785</v>
+        <v>2.59903</v>
       </c>
       <c r="N21">
-        <v>20.25758816666666</v>
+        <v>20.12763666666667</v>
       </c>
       <c r="O21">
-        <v>4.051517633333333</v>
+        <v>4.025527333333334</v>
       </c>
       <c r="P21">
-        <v>16.20607053333333</v>
+        <v>16.10210933333333</v>
       </c>
       <c r="Q21">
-        <v>20.94607053333333</v>
+        <v>20.84210933333333</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07738078447686417</v>
+        <v>0.07770906705978375</v>
       </c>
       <c r="T21">
-        <v>0.5990758117042722</v>
+        <v>0.6053032109943373</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.20451361374969</v>
+        <v>8.744287933062207</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.070727253647827</v>
+        <v>0.07064407186939403</v>
       </c>
       <c r="C22">
-        <v>191.5017757630316</v>
+        <v>189.5016555326659</v>
       </c>
       <c r="D22">
-        <v>226.4817757630317</v>
+        <v>226.910655532666</v>
       </c>
       <c r="E22">
-        <v>-82.31999999999999</v>
+        <v>-79.89099999999999</v>
       </c>
       <c r="F22">
-        <v>48.58000000000001</v>
+        <v>51.00900000000001</v>
       </c>
       <c r="G22">
         <v>13.6</v>
@@ -3079,28 +3079,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M22">
-        <v>2.59903</v>
+        <v>2.7289815</v>
       </c>
       <c r="N22">
-        <v>20.12763666666667</v>
+        <v>19.99768516666667</v>
       </c>
       <c r="O22">
-        <v>4.025527333333334</v>
+        <v>3.999537033333334</v>
       </c>
       <c r="P22">
-        <v>16.10210933333333</v>
+        <v>15.99814813333333</v>
       </c>
       <c r="Q22">
-        <v>20.84210933333333</v>
+        <v>20.73814813333333</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07770906705978375</v>
+        <v>0.07804566059416966</v>
       </c>
       <c r="T22">
-        <v>0.6053032109943373</v>
+        <v>0.611688265962632</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.744287933062207</v>
+        <v>8.327893269583054</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07064407186939403</v>
+        <v>0.07056089009096106</v>
       </c>
       <c r="C23">
-        <v>189.5016555326659</v>
+        <v>187.5031626900495</v>
       </c>
       <c r="D23">
-        <v>226.910655532666</v>
+        <v>227.3411626900495</v>
       </c>
       <c r="E23">
-        <v>-79.89100000000001</v>
+        <v>-77.462</v>
       </c>
       <c r="F23">
-        <v>51.009</v>
+        <v>53.438</v>
       </c>
       <c r="G23">
         <v>13.6</v>
@@ -3161,28 +3161,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M23">
-        <v>2.7289815</v>
+        <v>2.858933</v>
       </c>
       <c r="N23">
-        <v>19.99768516666667</v>
+        <v>19.86773366666667</v>
       </c>
       <c r="O23">
-        <v>3.999537033333334</v>
+        <v>3.973546733333333</v>
       </c>
       <c r="P23">
-        <v>15.99814813333333</v>
+        <v>15.89418693333333</v>
       </c>
       <c r="Q23">
-        <v>20.73814813333333</v>
+        <v>20.63418693333333</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07804566059416966</v>
+        <v>0.07839088473200136</v>
       </c>
       <c r="T23">
-        <v>0.611688265962632</v>
+        <v>0.6182370402890881</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.327893269583054</v>
+        <v>7.949352666420188</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07056089009096106</v>
+        <v>0.07062490831252809</v>
       </c>
       <c r="C24">
-        <v>187.5031626900495</v>
+        <v>184.7426918806261</v>
       </c>
       <c r="D24">
-        <v>227.3411626900495</v>
+        <v>227.0096918806261</v>
       </c>
       <c r="E24">
-        <v>-77.462</v>
+        <v>-75.033</v>
       </c>
       <c r="F24">
-        <v>53.438</v>
+        <v>55.867</v>
       </c>
       <c r="G24">
         <v>13.6</v>
@@ -3243,45 +3243,45 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M24">
-        <v>2.858933</v>
+        <v>3.0335781</v>
       </c>
       <c r="N24">
-        <v>19.86773366666667</v>
+        <v>19.69308856666667</v>
       </c>
       <c r="O24">
-        <v>3.973546733333333</v>
+        <v>3.938617713333334</v>
       </c>
       <c r="P24">
-        <v>15.89418693333333</v>
+        <v>15.75447085333333</v>
       </c>
       <c r="Q24">
-        <v>20.63418693333333</v>
+        <v>20.49447085333333</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07839088473200136</v>
+        <v>0.07874507573055595</v>
       </c>
       <c r="T24">
-        <v>0.6182370402890881</v>
+        <v>0.6249559126499976</v>
       </c>
       <c r="U24">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V24">
         <v>0.2</v>
       </c>
       <c r="W24">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y24">
-        <v>7.949352666420188</v>
+        <v>7.4917031694904</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07062490831252809</v>
+        <v>0.07054812653409512</v>
       </c>
       <c r="C25">
-        <v>184.7426918806261</v>
+        <v>182.7113650586683</v>
       </c>
       <c r="D25">
-        <v>227.0096918806261</v>
+        <v>227.4073650586683</v>
       </c>
       <c r="E25">
-        <v>-75.033</v>
+        <v>-72.604</v>
       </c>
       <c r="F25">
-        <v>55.867</v>
+        <v>58.29600000000001</v>
       </c>
       <c r="G25">
         <v>13.6</v>
@@ -3325,28 +3325,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M25">
-        <v>3.0335781</v>
+        <v>3.1654728</v>
       </c>
       <c r="N25">
-        <v>19.69308856666667</v>
+        <v>19.56119386666667</v>
       </c>
       <c r="O25">
-        <v>3.938617713333334</v>
+        <v>3.912238773333334</v>
       </c>
       <c r="P25">
-        <v>15.75447085333333</v>
+        <v>15.64895509333333</v>
       </c>
       <c r="Q25">
-        <v>20.49447085333333</v>
+        <v>20.38895509333333</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07874507573055595</v>
+        <v>0.079108587544862</v>
       </c>
       <c r="T25">
-        <v>0.6249559126499976</v>
+        <v>0.6318515974414575</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.4917031694904</v>
+        <v>7.179548870761633</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07054812653409512</v>
+        <v>0.07047134475566214</v>
       </c>
       <c r="C26">
-        <v>182.7113650586683</v>
+        <v>180.6814339610632</v>
       </c>
       <c r="D26">
-        <v>227.4073650586683</v>
+        <v>227.8064339610632</v>
       </c>
       <c r="E26">
-        <v>-72.60400000000001</v>
+        <v>-70.17500000000001</v>
       </c>
       <c r="F26">
-        <v>58.296</v>
+        <v>60.725</v>
       </c>
       <c r="G26">
         <v>13.6</v>
@@ -3407,28 +3407,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M26">
-        <v>3.1654728</v>
+        <v>3.2973675</v>
       </c>
       <c r="N26">
-        <v>19.56119386666667</v>
+        <v>19.42929916666667</v>
       </c>
       <c r="O26">
-        <v>3.912238773333334</v>
+        <v>3.885859833333333</v>
       </c>
       <c r="P26">
-        <v>15.64895509333333</v>
+        <v>15.54343933333333</v>
       </c>
       <c r="Q26">
-        <v>20.38895509333333</v>
+        <v>20.28343933333333</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.079108587544862</v>
+        <v>0.07948179300754951</v>
       </c>
       <c r="T26">
-        <v>0.6318515974414574</v>
+        <v>0.6389311671606893</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.179548870761634</v>
+        <v>6.892366915931168</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07047134475566214</v>
+        <v>0.07039456297722917</v>
       </c>
       <c r="C27">
-        <v>180.6814339610632</v>
+        <v>178.6529059486452</v>
       </c>
       <c r="D27">
-        <v>227.8064339610632</v>
+        <v>228.2069059486452</v>
       </c>
       <c r="E27">
-        <v>-70.17500000000001</v>
+        <v>-67.74600000000001</v>
       </c>
       <c r="F27">
-        <v>60.725</v>
+        <v>63.154</v>
       </c>
       <c r="G27">
         <v>13.6</v>
@@ -3489,28 +3489,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M27">
-        <v>3.2973675</v>
+        <v>3.4292622</v>
       </c>
       <c r="N27">
-        <v>19.42929916666667</v>
+        <v>19.29740446666667</v>
       </c>
       <c r="O27">
-        <v>3.885859833333333</v>
+        <v>3.859480893333334</v>
       </c>
       <c r="P27">
-        <v>15.54343933333333</v>
+        <v>15.43792357333333</v>
       </c>
       <c r="Q27">
-        <v>20.28343933333333</v>
+        <v>20.17792357333333</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07948179300754951</v>
+        <v>0.07986508510436374</v>
       </c>
       <c r="T27">
-        <v>0.6389311671606893</v>
+        <v>0.6462020766020629</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.892366915931168</v>
+        <v>6.627275880703047</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07039456297722917</v>
+        <v>0.0703177811987962</v>
       </c>
       <c r="C28">
-        <v>178.6529059486452</v>
+        <v>176.6257884341001</v>
       </c>
       <c r="D28">
-        <v>228.2069059486452</v>
+        <v>228.6087884341001</v>
       </c>
       <c r="E28">
-        <v>-67.74600000000001</v>
+        <v>-65.31699999999999</v>
       </c>
       <c r="F28">
-        <v>63.154</v>
+        <v>65.58300000000001</v>
       </c>
       <c r="G28">
         <v>13.6</v>
@@ -3571,28 +3571,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M28">
-        <v>3.4292622</v>
+        <v>3.561156900000001</v>
       </c>
       <c r="N28">
-        <v>19.29740446666667</v>
+        <v>19.16550976666667</v>
       </c>
       <c r="O28">
-        <v>3.859480893333334</v>
+        <v>3.833101953333333</v>
       </c>
       <c r="P28">
-        <v>15.43792357333333</v>
+        <v>15.33240781333333</v>
       </c>
       <c r="Q28">
-        <v>20.17792357333333</v>
+        <v>20.07240781333334</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07986508510436374</v>
+        <v>0.08025887835451534</v>
       </c>
       <c r="T28">
-        <v>0.6462020766020629</v>
+        <v>0.6536721890418301</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.627275880703047</v>
+        <v>6.381821218454784</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0703177811987962</v>
+        <v>0.07024099942036323</v>
       </c>
       <c r="C29">
-        <v>176.6257884341001</v>
+        <v>174.6000888824223</v>
       </c>
       <c r="D29">
-        <v>228.6087884341001</v>
+        <v>229.0120888824223</v>
       </c>
       <c r="E29">
-        <v>-65.31699999999999</v>
+        <v>-62.88799999999999</v>
       </c>
       <c r="F29">
-        <v>65.58300000000001</v>
+        <v>68.01200000000001</v>
       </c>
       <c r="G29">
         <v>13.6</v>
@@ -3653,28 +3653,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M29">
-        <v>3.561156900000001</v>
+        <v>3.693051600000001</v>
       </c>
       <c r="N29">
-        <v>19.16550976666667</v>
+        <v>19.03361506666667</v>
       </c>
       <c r="O29">
-        <v>3.833101953333333</v>
+        <v>3.806723013333333</v>
       </c>
       <c r="P29">
-        <v>15.33240781333333</v>
+        <v>15.22689205333333</v>
       </c>
       <c r="Q29">
-        <v>20.07240781333334</v>
+        <v>19.96689205333333</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08025887835451534</v>
+        <v>0.08066361030606004</v>
       </c>
       <c r="T29">
-        <v>0.6536721890418301</v>
+        <v>0.6613498046049241</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.381821218454784</v>
+        <v>6.153899032081399</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07024099942036323</v>
+        <v>0.07039621764193024</v>
       </c>
       <c r="C30">
-        <v>174.6000888824223</v>
+        <v>171.3572608426417</v>
       </c>
       <c r="D30">
-        <v>229.0120888824223</v>
+        <v>228.1982608426417</v>
       </c>
       <c r="E30">
-        <v>-62.88799999999999</v>
+        <v>-60.45899999999999</v>
       </c>
       <c r="F30">
-        <v>68.01200000000001</v>
+        <v>70.44100000000002</v>
       </c>
       <c r="G30">
         <v>13.6</v>
@@ -3735,45 +3735,45 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M30">
-        <v>3.693051600000001</v>
+        <v>3.895387300000001</v>
       </c>
       <c r="N30">
-        <v>19.03361506666667</v>
+        <v>18.83127936666666</v>
       </c>
       <c r="O30">
-        <v>3.806723013333333</v>
+        <v>3.766255873333333</v>
       </c>
       <c r="P30">
-        <v>15.22689205333333</v>
+        <v>15.06502349333333</v>
       </c>
       <c r="Q30">
-        <v>19.96689205333333</v>
+        <v>19.80502349333333</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08066361030606004</v>
+        <v>0.08107974315764824</v>
       </c>
       <c r="T30">
-        <v>0.6613498046049241</v>
+        <v>0.6692436910289504</v>
       </c>
       <c r="U30">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V30">
         <v>0.2</v>
       </c>
       <c r="W30">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>6.153899032081399</v>
+        <v>5.834250850144389</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07039621764193024</v>
+        <v>0.07032743586349727</v>
       </c>
       <c r="C31">
-        <v>171.3572608426417</v>
+        <v>169.2881772976566</v>
       </c>
       <c r="D31">
-        <v>228.1982608426417</v>
+        <v>228.5581772976566</v>
       </c>
       <c r="E31">
-        <v>-60.459</v>
+        <v>-58.03</v>
       </c>
       <c r="F31">
-        <v>70.441</v>
+        <v>72.87</v>
       </c>
       <c r="G31">
         <v>13.6</v>
@@ -3817,28 +3817,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M31">
-        <v>3.8953873</v>
+        <v>4.029711000000001</v>
       </c>
       <c r="N31">
-        <v>18.83127936666667</v>
+        <v>18.69695566666667</v>
       </c>
       <c r="O31">
-        <v>3.766255873333334</v>
+        <v>3.739391133333334</v>
       </c>
       <c r="P31">
-        <v>15.06502349333333</v>
+        <v>14.95756453333333</v>
       </c>
       <c r="Q31">
-        <v>19.80502349333333</v>
+        <v>19.69756453333333</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08107974315764824</v>
+        <v>0.08150776551928182</v>
       </c>
       <c r="T31">
-        <v>0.6692436910289504</v>
+        <v>0.6773631170650918</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.834250850144391</v>
+        <v>5.639775821806245</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07032743586349727</v>
+        <v>0.07025865408506429</v>
       </c>
       <c r="C32">
-        <v>169.2881772976566</v>
+        <v>167.2202308734221</v>
       </c>
       <c r="D32">
-        <v>228.5581772976566</v>
+        <v>228.9192308734221</v>
       </c>
       <c r="E32">
-        <v>-58.03</v>
+        <v>-55.601</v>
       </c>
       <c r="F32">
-        <v>72.87</v>
+        <v>75.29900000000001</v>
       </c>
       <c r="G32">
         <v>13.6</v>
@@ -3899,28 +3899,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M32">
-        <v>4.029711000000001</v>
+        <v>4.1640347</v>
       </c>
       <c r="N32">
-        <v>18.69695566666667</v>
+        <v>18.56263196666666</v>
       </c>
       <c r="O32">
-        <v>3.739391133333334</v>
+        <v>3.712526393333333</v>
       </c>
       <c r="P32">
-        <v>14.95756453333333</v>
+        <v>14.85010557333333</v>
       </c>
       <c r="Q32">
-        <v>19.69756453333333</v>
+        <v>19.59010557333333</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08150776551928182</v>
+        <v>0.08194819432618014</v>
       </c>
       <c r="T32">
-        <v>0.6773631170650918</v>
+        <v>0.6857178887834401</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.639775821806245</v>
+        <v>5.457847569489914</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07025865408506429</v>
+        <v>0.07018987230663132</v>
       </c>
       <c r="C33">
-        <v>167.2202308734221</v>
+        <v>165.1534269673968</v>
       </c>
       <c r="D33">
-        <v>228.9192308734221</v>
+        <v>229.2814269673968</v>
       </c>
       <c r="E33">
-        <v>-55.601</v>
+        <v>-53.172</v>
       </c>
       <c r="F33">
-        <v>75.29900000000001</v>
+        <v>77.72800000000001</v>
       </c>
       <c r="G33">
         <v>13.6</v>
@@ -3981,28 +3981,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M33">
-        <v>4.1640347</v>
+        <v>4.298358400000001</v>
       </c>
       <c r="N33">
-        <v>18.56263196666666</v>
+        <v>18.42830826666667</v>
       </c>
       <c r="O33">
-        <v>3.712526393333333</v>
+        <v>3.685661653333333</v>
       </c>
       <c r="P33">
-        <v>14.85010557333333</v>
+        <v>14.74264661333333</v>
       </c>
       <c r="Q33">
-        <v>19.59010557333333</v>
+        <v>19.48264661333333</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08194819432618014</v>
+        <v>0.08240157692151666</v>
       </c>
       <c r="T33">
-        <v>0.6857178887834401</v>
+        <v>0.6943183890817398</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.457847569489914</v>
+        <v>5.287289832943354</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07018987230663132</v>
+        <v>0.07012109052819836</v>
       </c>
       <c r="C34">
-        <v>165.1534269673968</v>
+        <v>163.0877710112529</v>
       </c>
       <c r="D34">
-        <v>229.2814269673968</v>
+        <v>229.6447710112529</v>
       </c>
       <c r="E34">
-        <v>-53.172</v>
+        <v>-50.74299999999999</v>
       </c>
       <c r="F34">
-        <v>77.72800000000001</v>
+        <v>80.15700000000001</v>
       </c>
       <c r="G34">
         <v>13.6</v>
@@ -4063,28 +4063,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M34">
-        <v>4.298358400000001</v>
+        <v>4.432682100000001</v>
       </c>
       <c r="N34">
-        <v>18.42830826666667</v>
+        <v>18.29398456666667</v>
       </c>
       <c r="O34">
-        <v>3.685661653333333</v>
+        <v>3.658796913333333</v>
       </c>
       <c r="P34">
-        <v>14.74264661333333</v>
+        <v>14.63518765333333</v>
       </c>
       <c r="Q34">
-        <v>19.48264661333333</v>
+        <v>19.37518765333333</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08240157692151666</v>
+        <v>0.0828684933256692</v>
       </c>
       <c r="T34">
-        <v>0.6943183890817398</v>
+        <v>0.7031756207322277</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.287289832943354</v>
+        <v>5.127068928914768</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07012109052819836</v>
+        <v>0.07005230874976538</v>
       </c>
       <c r="C35">
-        <v>163.0877710112529</v>
+        <v>161.0232684711479</v>
       </c>
       <c r="D35">
-        <v>229.6447710112529</v>
+        <v>230.0092684711479</v>
       </c>
       <c r="E35">
-        <v>-50.74299999999999</v>
+        <v>-48.31399999999999</v>
       </c>
       <c r="F35">
-        <v>80.15700000000001</v>
+        <v>82.58600000000001</v>
       </c>
       <c r="G35">
         <v>13.6</v>
@@ -4145,28 +4145,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M35">
-        <v>4.432682100000001</v>
+        <v>4.5670058</v>
       </c>
       <c r="N35">
-        <v>18.29398456666667</v>
+        <v>18.15966086666667</v>
       </c>
       <c r="O35">
-        <v>3.658796913333333</v>
+        <v>3.631932173333333</v>
       </c>
       <c r="P35">
-        <v>14.63518765333333</v>
+        <v>14.52772869333333</v>
       </c>
       <c r="Q35">
-        <v>19.37518765333333</v>
+        <v>19.26772869333333</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.0828684933256692</v>
+        <v>0.08334955871176573</v>
       </c>
       <c r="T35">
-        <v>0.7031756207322277</v>
+        <v>0.7123012533418212</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.127068928914768</v>
+        <v>4.976272783946687</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07005230874976538</v>
+        <v>0.06998352697133241</v>
       </c>
       <c r="C36">
-        <v>161.0232684711479</v>
+        <v>158.9599248479982</v>
       </c>
       <c r="D36">
-        <v>230.0092684711479</v>
+        <v>230.3749248479982</v>
       </c>
       <c r="E36">
-        <v>-48.31399999999999</v>
+        <v>-45.88499999999999</v>
       </c>
       <c r="F36">
-        <v>82.58600000000001</v>
+        <v>85.01500000000001</v>
       </c>
       <c r="G36">
         <v>13.6</v>
@@ -4227,28 +4227,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M36">
-        <v>4.5670058</v>
+        <v>4.701329500000001</v>
       </c>
       <c r="N36">
-        <v>18.15966086666667</v>
+        <v>18.02533716666667</v>
       </c>
       <c r="O36">
-        <v>3.631932173333333</v>
+        <v>3.605067433333334</v>
       </c>
       <c r="P36">
-        <v>14.52772869333333</v>
+        <v>14.42026973333333</v>
       </c>
       <c r="Q36">
-        <v>19.26772869333333</v>
+        <v>19.16026973333333</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08334955871176573</v>
+        <v>0.08384542610974217</v>
       </c>
       <c r="T36">
-        <v>0.7123012533418212</v>
+        <v>0.7217076746470945</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.976272783946687</v>
+        <v>4.83409356154821</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06998352697133241</v>
+        <v>0.06991474519289943</v>
       </c>
       <c r="C37">
-        <v>158.9599248479982</v>
+        <v>156.8977456777563</v>
       </c>
       <c r="D37">
-        <v>230.3749248479982</v>
+        <v>230.7417456777563</v>
       </c>
       <c r="E37">
-        <v>-45.88499999999999</v>
+        <v>-43.45599999999999</v>
       </c>
       <c r="F37">
-        <v>85.01500000000001</v>
+        <v>87.44400000000002</v>
       </c>
       <c r="G37">
         <v>13.6</v>
@@ -4309,28 +4309,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M37">
-        <v>4.701329500000001</v>
+        <v>4.835653200000001</v>
       </c>
       <c r="N37">
-        <v>18.02533716666667</v>
+        <v>17.89101346666666</v>
       </c>
       <c r="O37">
-        <v>3.605067433333334</v>
+        <v>3.578202693333333</v>
       </c>
       <c r="P37">
-        <v>14.42026973333333</v>
+        <v>14.31281077333333</v>
       </c>
       <c r="Q37">
-        <v>19.16026973333333</v>
+        <v>19.05281077333333</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08384542610974217</v>
+        <v>0.08435678936390537</v>
       </c>
       <c r="T37">
-        <v>0.7217076746470945</v>
+        <v>0.7314080466181576</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.83409356154821</v>
+        <v>4.699813184838536</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06991474519289943</v>
+        <v>0.06984596341446647</v>
       </c>
       <c r="C38">
-        <v>156.8977456777563</v>
+        <v>154.83673653169</v>
       </c>
       <c r="D38">
-        <v>230.7417456777563</v>
+        <v>231.1097365316899</v>
       </c>
       <c r="E38">
-        <v>-43.456</v>
+        <v>-41.027</v>
       </c>
       <c r="F38">
-        <v>87.444</v>
+        <v>89.873</v>
       </c>
       <c r="G38">
         <v>13.6</v>
@@ -4391,28 +4391,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M38">
-        <v>4.8356532</v>
+        <v>4.969976900000001</v>
       </c>
       <c r="N38">
-        <v>17.89101346666667</v>
+        <v>17.75668976666667</v>
       </c>
       <c r="O38">
-        <v>3.578202693333334</v>
+        <v>3.551337953333334</v>
       </c>
       <c r="P38">
-        <v>14.31281077333333</v>
+        <v>14.20535181333333</v>
       </c>
       <c r="Q38">
-        <v>19.05281077333333</v>
+        <v>18.94535181333333</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08435678936390537</v>
+        <v>0.084884386372169</v>
       </c>
       <c r="T38">
-        <v>0.7314080466181575</v>
+        <v>0.7414163669057624</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.699813184838538</v>
+        <v>4.572791206869928</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06984596341446647</v>
+        <v>0.07053718163603349</v>
       </c>
       <c r="C39">
-        <v>154.83673653169</v>
+        <v>148.7621650725551</v>
       </c>
       <c r="D39">
-        <v>231.1097365316899</v>
+        <v>227.4641650725551</v>
       </c>
       <c r="E39">
-        <v>-41.027</v>
+        <v>-38.598</v>
       </c>
       <c r="F39">
-        <v>89.873</v>
+        <v>92.30200000000001</v>
       </c>
       <c r="G39">
         <v>13.6</v>
@@ -4473,45 +4473,45 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M39">
-        <v>4.969976900000001</v>
+        <v>5.3350556</v>
       </c>
       <c r="N39">
-        <v>17.75668976666667</v>
+        <v>17.39161106666667</v>
       </c>
       <c r="O39">
-        <v>3.551337953333334</v>
+        <v>3.478322213333334</v>
       </c>
       <c r="P39">
-        <v>14.20535181333333</v>
+        <v>13.91328885333333</v>
       </c>
       <c r="Q39">
-        <v>18.94535181333333</v>
+        <v>18.65328885333333</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.084884386372169</v>
+        <v>0.0854290026387637</v>
       </c>
       <c r="T39">
-        <v>0.7414163669057624</v>
+        <v>0.7517475362349028</v>
       </c>
       <c r="U39">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V39">
         <v>0.2</v>
       </c>
       <c r="W39">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>4.572791206869928</v>
+        <v>4.259874380065817</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07053718163603349</v>
+        <v>0.07048839985760053</v>
       </c>
       <c r="C40">
-        <v>148.7621650725551</v>
+        <v>146.586670087835</v>
       </c>
       <c r="D40">
-        <v>227.4641650725551</v>
+        <v>227.717670087835</v>
       </c>
       <c r="E40">
-        <v>-38.598</v>
+        <v>-36.169</v>
       </c>
       <c r="F40">
-        <v>92.30200000000001</v>
+        <v>94.73100000000001</v>
       </c>
       <c r="G40">
         <v>13.6</v>
@@ -4555,28 +4555,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M40">
-        <v>5.3350556</v>
+        <v>5.475451800000001</v>
       </c>
       <c r="N40">
-        <v>17.39161106666667</v>
+        <v>17.25121486666666</v>
       </c>
       <c r="O40">
-        <v>3.478322213333334</v>
+        <v>3.450242973333333</v>
       </c>
       <c r="P40">
-        <v>13.91328885333333</v>
+        <v>13.80097189333333</v>
       </c>
       <c r="Q40">
-        <v>18.65328885333333</v>
+        <v>18.54097189333333</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.0854290026387637</v>
+        <v>0.0859914751763943</v>
       </c>
       <c r="T40">
-        <v>0.7517475362349028</v>
+        <v>0.7624174324272938</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.259874380065817</v>
+        <v>4.150646831859</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07048839985760053</v>
+        <v>0.07043961807916756</v>
       </c>
       <c r="C41">
-        <v>146.586670087835</v>
+        <v>144.4117407877774</v>
       </c>
       <c r="D41">
-        <v>227.717670087835</v>
+        <v>227.9717407877775</v>
       </c>
       <c r="E41">
-        <v>-36.169</v>
+        <v>-33.73999999999999</v>
       </c>
       <c r="F41">
-        <v>94.73100000000001</v>
+        <v>97.16000000000001</v>
       </c>
       <c r="G41">
         <v>13.6</v>
@@ -4637,28 +4637,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M41">
-        <v>5.475451800000001</v>
+        <v>5.615848000000001</v>
       </c>
       <c r="N41">
-        <v>17.25121486666666</v>
+        <v>17.11081866666667</v>
       </c>
       <c r="O41">
-        <v>3.450242973333333</v>
+        <v>3.422163733333333</v>
       </c>
       <c r="P41">
-        <v>13.80097189333333</v>
+        <v>13.68865493333333</v>
       </c>
       <c r="Q41">
-        <v>18.54097189333333</v>
+        <v>18.42865493333333</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.0859914751763943</v>
+        <v>0.08657269679861258</v>
       </c>
       <c r="T41">
-        <v>0.7624174324272938</v>
+        <v>0.7734429918260978</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.150646831859</v>
+        <v>4.046880661062525</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07043961807916756</v>
+        <v>0.07153883630073457</v>
       </c>
       <c r="C42">
-        <v>144.4117407877774</v>
+        <v>136.3918434808626</v>
       </c>
       <c r="D42">
-        <v>227.9717407877775</v>
+        <v>222.3808434808626</v>
       </c>
       <c r="E42">
-        <v>-33.73999999999999</v>
+        <v>-31.31099999999999</v>
       </c>
       <c r="F42">
-        <v>97.16000000000001</v>
+        <v>99.58900000000001</v>
       </c>
       <c r="G42">
         <v>13.6</v>
@@ -4719,45 +4719,45 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M42">
-        <v>5.615848000000001</v>
+        <v>6.104805700000001</v>
       </c>
       <c r="N42">
-        <v>17.11081866666667</v>
+        <v>16.62186096666667</v>
       </c>
       <c r="O42">
-        <v>3.422163733333333</v>
+        <v>3.324372193333334</v>
       </c>
       <c r="P42">
-        <v>13.68865493333333</v>
+        <v>13.29748877333333</v>
       </c>
       <c r="Q42">
-        <v>18.42865493333333</v>
+        <v>18.03748877333333</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08657269679861258</v>
+        <v>0.08717362084870267</v>
       </c>
       <c r="T42">
-        <v>0.7734429918260978</v>
+        <v>0.7848422990011323</v>
       </c>
       <c r="U42">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V42">
         <v>0.2</v>
       </c>
       <c r="W42">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.046880661062525</v>
+        <v>3.72275020426394</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07153883630073457</v>
+        <v>0.0715180545223016</v>
       </c>
       <c r="C43">
-        <v>136.3918434808626</v>
+        <v>134.0660003317199</v>
       </c>
       <c r="D43">
-        <v>222.3808434808626</v>
+        <v>222.4840003317199</v>
       </c>
       <c r="E43">
-        <v>-31.31099999999999</v>
+        <v>-28.88199999999999</v>
       </c>
       <c r="F43">
-        <v>99.58900000000001</v>
+        <v>102.018</v>
       </c>
       <c r="G43">
         <v>13.6</v>
@@ -4801,28 +4801,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M43">
-        <v>6.104805700000001</v>
+        <v>6.253703400000001</v>
       </c>
       <c r="N43">
-        <v>16.62186096666667</v>
+        <v>16.47296326666667</v>
       </c>
       <c r="O43">
-        <v>3.324372193333334</v>
+        <v>3.294592653333334</v>
       </c>
       <c r="P43">
-        <v>13.29748877333333</v>
+        <v>13.17837061333333</v>
       </c>
       <c r="Q43">
-        <v>18.03748877333333</v>
+        <v>17.91837061333333</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08717362084870267</v>
+        <v>0.08779526641776139</v>
       </c>
       <c r="T43">
-        <v>0.7848422990011323</v>
+        <v>0.7966346857339268</v>
       </c>
       <c r="U43">
         <v>0.0613</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.72275020426394</v>
+        <v>3.634113294638608</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0715180545223016</v>
+        <v>0.07149727274386863</v>
       </c>
       <c r="C44">
-        <v>134.0660003317199</v>
+        <v>131.7402529307023</v>
       </c>
       <c r="D44">
-        <v>222.4840003317199</v>
+        <v>222.5872529307023</v>
       </c>
       <c r="E44">
-        <v>-28.88200000000001</v>
+        <v>-26.453</v>
       </c>
       <c r="F44">
-        <v>102.018</v>
+        <v>104.447</v>
       </c>
       <c r="G44">
         <v>13.6</v>
@@ -4883,28 +4883,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M44">
-        <v>6.2537034</v>
+        <v>6.4026011</v>
       </c>
       <c r="N44">
-        <v>16.47296326666667</v>
+        <v>16.32406556666667</v>
       </c>
       <c r="O44">
-        <v>3.294592653333334</v>
+        <v>3.264813113333334</v>
       </c>
       <c r="P44">
-        <v>13.17837061333333</v>
+        <v>13.05925245333333</v>
       </c>
       <c r="Q44">
-        <v>17.91837061333333</v>
+        <v>17.79925245333333</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08779526641776138</v>
+        <v>0.08843872411205023</v>
       </c>
       <c r="T44">
-        <v>0.7966346857339266</v>
+        <v>0.8088408404222578</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.634113294638608</v>
+        <v>3.549599031972595</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07149727274386863</v>
+        <v>0.07246209096543567</v>
       </c>
       <c r="C45">
-        <v>131.7402529307023</v>
+        <v>124.6165578383058</v>
       </c>
       <c r="D45">
-        <v>222.5872529307023</v>
+        <v>217.8925578383058</v>
       </c>
       <c r="E45">
-        <v>-26.453</v>
+        <v>-24.024</v>
       </c>
       <c r="F45">
-        <v>104.447</v>
+        <v>106.876</v>
       </c>
       <c r="G45">
         <v>13.6</v>
@@ -4965,45 +4965,45 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M45">
-        <v>6.4026011</v>
+        <v>6.850751600000001</v>
       </c>
       <c r="N45">
-        <v>16.32406556666667</v>
+        <v>15.87591506666667</v>
       </c>
       <c r="O45">
-        <v>3.264813113333334</v>
+        <v>3.175183013333333</v>
       </c>
       <c r="P45">
-        <v>13.05925245333333</v>
+        <v>12.70073205333333</v>
       </c>
       <c r="Q45">
-        <v>17.79925245333333</v>
+        <v>17.44073205333333</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08843872411205023</v>
+        <v>0.08910516243827796</v>
       </c>
       <c r="T45">
-        <v>0.8088408404222578</v>
+        <v>0.8214829292066006</v>
       </c>
       <c r="U45">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V45">
         <v>0.2</v>
       </c>
       <c r="W45">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.549599031972595</v>
+        <v>3.317397563599688</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07246209096543567</v>
+        <v>0.07246370918700269</v>
       </c>
       <c r="C46">
-        <v>124.6165578383058</v>
+        <v>122.1798501059858</v>
       </c>
       <c r="D46">
-        <v>217.8925578383058</v>
+        <v>217.8848501059858</v>
       </c>
       <c r="E46">
-        <v>-24.024</v>
+        <v>-21.595</v>
       </c>
       <c r="F46">
-        <v>106.876</v>
+        <v>109.305</v>
       </c>
       <c r="G46">
         <v>13.6</v>
@@ -5047,28 +5047,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M46">
-        <v>6.850751600000001</v>
+        <v>7.006450500000001</v>
       </c>
       <c r="N46">
-        <v>15.87591506666667</v>
+        <v>15.72021616666667</v>
       </c>
       <c r="O46">
-        <v>3.175183013333333</v>
+        <v>3.144043233333333</v>
       </c>
       <c r="P46">
-        <v>12.70073205333333</v>
+        <v>12.57617293333333</v>
       </c>
       <c r="Q46">
-        <v>17.44073205333333</v>
+        <v>17.31617293333333</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08910516243827796</v>
+        <v>0.08979583488545942</v>
       </c>
       <c r="T46">
-        <v>0.8214829292066006</v>
+        <v>0.8345847303103742</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.317397563599688</v>
+        <v>3.243677617741918</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07246370918700269</v>
+        <v>0.07246532740856972</v>
       </c>
       <c r="C47">
-        <v>122.1798501059858</v>
+        <v>119.7431429189533</v>
       </c>
       <c r="D47">
-        <v>217.8848501059858</v>
+        <v>217.8771429189533</v>
       </c>
       <c r="E47">
-        <v>-21.595</v>
+        <v>-19.166</v>
       </c>
       <c r="F47">
-        <v>109.305</v>
+        <v>111.734</v>
       </c>
       <c r="G47">
         <v>13.6</v>
@@ -5129,28 +5129,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M47">
-        <v>7.006450500000001</v>
+        <v>7.162149400000001</v>
       </c>
       <c r="N47">
-        <v>15.72021616666667</v>
+        <v>15.56451726666667</v>
       </c>
       <c r="O47">
-        <v>3.144043233333333</v>
+        <v>3.112903453333333</v>
       </c>
       <c r="P47">
-        <v>12.57617293333333</v>
+        <v>12.45161381333333</v>
       </c>
       <c r="Q47">
-        <v>17.31617293333333</v>
+        <v>17.19161381333333</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08979583488545942</v>
+        <v>0.09051208779364761</v>
       </c>
       <c r="T47">
-        <v>0.8345847303103742</v>
+        <v>0.8481717833068801</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.243677617741918</v>
+        <v>3.17316288692144</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07246532740856972</v>
+        <v>0.07246694563013674</v>
       </c>
       <c r="C48">
-        <v>119.7431429189533</v>
+        <v>117.3064362771503</v>
       </c>
       <c r="D48">
-        <v>217.8771429189533</v>
+        <v>217.8694362771503</v>
       </c>
       <c r="E48">
-        <v>-19.166</v>
+        <v>-16.73699999999999</v>
       </c>
       <c r="F48">
-        <v>111.734</v>
+        <v>114.163</v>
       </c>
       <c r="G48">
         <v>13.6</v>
@@ -5211,28 +5211,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M48">
-        <v>7.162149400000001</v>
+        <v>7.317848300000001</v>
       </c>
       <c r="N48">
-        <v>15.56451726666667</v>
+        <v>15.40881836666667</v>
       </c>
       <c r="O48">
-        <v>3.112903453333333</v>
+        <v>3.081763673333333</v>
       </c>
       <c r="P48">
-        <v>12.45161381333333</v>
+        <v>12.32705469333333</v>
       </c>
       <c r="Q48">
-        <v>17.19161381333333</v>
+        <v>17.06705469333333</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09051208779364761</v>
+        <v>0.09125536911346555</v>
       </c>
       <c r="T48">
-        <v>0.8481717833068801</v>
+        <v>0.8622715552843861</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.17316288692144</v>
+        <v>3.105648782944388</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07246694563013674</v>
+        <v>0.07246856385170376</v>
       </c>
       <c r="C49">
-        <v>117.3064362771503</v>
+        <v>114.869730180519</v>
       </c>
       <c r="D49">
-        <v>217.8694362771503</v>
+        <v>217.861730180519</v>
       </c>
       <c r="E49">
-        <v>-16.73699999999999</v>
+        <v>-14.30799999999999</v>
       </c>
       <c r="F49">
-        <v>114.163</v>
+        <v>116.592</v>
       </c>
       <c r="G49">
         <v>13.6</v>
@@ -5293,28 +5293,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M49">
-        <v>7.317848300000001</v>
+        <v>7.473547200000001</v>
       </c>
       <c r="N49">
-        <v>15.40881836666667</v>
+        <v>15.25311946666666</v>
       </c>
       <c r="O49">
-        <v>3.081763673333333</v>
+        <v>3.050623893333333</v>
       </c>
       <c r="P49">
-        <v>12.32705469333333</v>
+        <v>12.20249557333333</v>
       </c>
       <c r="Q49">
-        <v>17.06705469333333</v>
+        <v>16.94249557333333</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09125536911346555</v>
+        <v>0.09202723817635339</v>
       </c>
       <c r="T49">
-        <v>0.8622715552843861</v>
+        <v>0.8769136261841041</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.105648782944388</v>
+        <v>3.040947766633047</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07246856385170376</v>
+        <v>0.07552778207327079</v>
       </c>
       <c r="C50">
-        <v>114.869730180519</v>
+        <v>98.78605553389981</v>
       </c>
       <c r="D50">
-        <v>217.861730180519</v>
+        <v>204.2070555338998</v>
       </c>
       <c r="E50">
-        <v>-14.30800000000001</v>
+        <v>-11.879</v>
       </c>
       <c r="F50">
-        <v>116.592</v>
+        <v>119.021</v>
       </c>
       <c r="G50">
         <v>13.6</v>
@@ -5375,45 +5375,45 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M50">
-        <v>7.473547200000001</v>
+        <v>8.557609900000001</v>
       </c>
       <c r="N50">
-        <v>15.25311946666667</v>
+        <v>14.16905676666667</v>
       </c>
       <c r="O50">
-        <v>3.050623893333333</v>
+        <v>2.833811353333333</v>
       </c>
       <c r="P50">
-        <v>12.20249557333333</v>
+        <v>11.33524541333333</v>
       </c>
       <c r="Q50">
-        <v>16.94249557333333</v>
+        <v>16.07524541333333</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09202723817635339</v>
+        <v>0.09282937661425644</v>
       </c>
       <c r="T50">
-        <v>0.8769136261841041</v>
+        <v>0.8921298959426344</v>
       </c>
       <c r="U50">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V50">
         <v>0.2</v>
       </c>
       <c r="W50">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.040947766633047</v>
+        <v>2.655725948277528</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07552778207327079</v>
+        <v>0.07559180029483782</v>
       </c>
       <c r="C51">
-        <v>98.78605553389981</v>
+        <v>96.08957322570468</v>
       </c>
       <c r="D51">
-        <v>204.2070555338998</v>
+        <v>203.9395732257047</v>
       </c>
       <c r="E51">
-        <v>-11.879</v>
+        <v>-9.450000000000003</v>
       </c>
       <c r="F51">
-        <v>119.021</v>
+        <v>121.45</v>
       </c>
       <c r="G51">
         <v>13.6</v>
@@ -5457,28 +5457,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M51">
-        <v>8.557609900000001</v>
+        <v>8.732255</v>
       </c>
       <c r="N51">
-        <v>14.16905676666667</v>
+        <v>13.99441166666667</v>
       </c>
       <c r="O51">
-        <v>2.833811353333333</v>
+        <v>2.798882333333333</v>
       </c>
       <c r="P51">
-        <v>11.33524541333333</v>
+        <v>11.19552933333333</v>
       </c>
       <c r="Q51">
-        <v>16.07524541333333</v>
+        <v>15.93552933333333</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09282937661425644</v>
+        <v>0.09366360058967563</v>
       </c>
       <c r="T51">
-        <v>0.8921298959426344</v>
+        <v>0.907954816491506</v>
       </c>
       <c r="U51">
         <v>0.07190000000000001</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.655725948277528</v>
+        <v>2.602611429311978</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07559180029483782</v>
+        <v>0.07565581851640485</v>
       </c>
       <c r="C52">
-        <v>96.08957322570468</v>
+        <v>93.39379072870319</v>
       </c>
       <c r="D52">
-        <v>203.9395732257047</v>
+        <v>203.6727907287032</v>
       </c>
       <c r="E52">
-        <v>-9.450000000000003</v>
+        <v>-7.021000000000001</v>
       </c>
       <c r="F52">
-        <v>121.45</v>
+        <v>123.879</v>
       </c>
       <c r="G52">
         <v>13.6</v>
@@ -5539,28 +5539,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M52">
-        <v>8.732255</v>
+        <v>8.906900100000001</v>
       </c>
       <c r="N52">
-        <v>13.99441166666667</v>
+        <v>13.81976656666667</v>
       </c>
       <c r="O52">
-        <v>2.798882333333333</v>
+        <v>2.763953313333333</v>
       </c>
       <c r="P52">
-        <v>11.19552933333333</v>
+        <v>11.05581325333333</v>
       </c>
       <c r="Q52">
-        <v>15.93552933333333</v>
+        <v>15.79581325333333</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09366360058967563</v>
+        <v>0.09453187452327519</v>
       </c>
       <c r="T52">
-        <v>0.907954816491506</v>
+        <v>0.9244256521648213</v>
       </c>
       <c r="U52">
         <v>0.07190000000000001</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.602611429311978</v>
+        <v>2.551579832658802</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07565581851640485</v>
+        <v>0.07571983673797188</v>
       </c>
       <c r="C53">
-        <v>93.39379072870319</v>
+        <v>90.6987053001201</v>
       </c>
       <c r="D53">
-        <v>203.6727907287032</v>
+        <v>203.4067053001201</v>
       </c>
       <c r="E53">
-        <v>-7.021000000000001</v>
+        <v>-4.591999999999999</v>
       </c>
       <c r="F53">
-        <v>123.879</v>
+        <v>126.308</v>
       </c>
       <c r="G53">
         <v>13.6</v>
@@ -5621,28 +5621,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M53">
-        <v>8.906900100000001</v>
+        <v>9.081545200000001</v>
       </c>
       <c r="N53">
-        <v>13.81976656666667</v>
+        <v>13.64512146666667</v>
       </c>
       <c r="O53">
-        <v>2.763953313333333</v>
+        <v>2.729024293333334</v>
       </c>
       <c r="P53">
-        <v>11.05581325333333</v>
+        <v>10.91609717333333</v>
       </c>
       <c r="Q53">
-        <v>15.79581325333333</v>
+        <v>15.65609717333333</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09453187452327519</v>
+        <v>0.0954363265374414</v>
       </c>
       <c r="T53">
-        <v>0.9244256521648213</v>
+        <v>0.9415827726578581</v>
       </c>
       <c r="U53">
         <v>0.07190000000000001</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.551579832658802</v>
+        <v>2.502510989723056</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07571983673797188</v>
+        <v>0.07743745495953891</v>
       </c>
       <c r="C54">
-        <v>90.6987053001201</v>
+        <v>81.3813702144362</v>
       </c>
       <c r="D54">
-        <v>203.4067053001201</v>
+        <v>196.5183702144362</v>
       </c>
       <c r="E54">
-        <v>-4.591999999999999</v>
+        <v>-2.162999999999982</v>
       </c>
       <c r="F54">
-        <v>126.308</v>
+        <v>128.737</v>
       </c>
       <c r="G54">
         <v>13.6</v>
@@ -5703,45 +5703,45 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M54">
-        <v>9.081545200000001</v>
+        <v>9.758264600000002</v>
       </c>
       <c r="N54">
-        <v>13.64512146666667</v>
+        <v>12.96840206666666</v>
       </c>
       <c r="O54">
-        <v>2.729024293333334</v>
+        <v>2.593680413333333</v>
       </c>
       <c r="P54">
-        <v>10.91609717333333</v>
+        <v>10.37472165333333</v>
       </c>
       <c r="Q54">
-        <v>15.65609717333333</v>
+        <v>15.11472165333333</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.0954363265374414</v>
+        <v>0.09637926587135937</v>
       </c>
       <c r="T54">
-        <v>0.9415827726578581</v>
+        <v>0.9594699833846412</v>
       </c>
       <c r="U54">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V54">
         <v>0.2</v>
       </c>
       <c r="W54">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.502510989723056</v>
+        <v>2.328966019907542</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07743745495953891</v>
+        <v>0.07753267318110593</v>
       </c>
       <c r="C55">
-        <v>81.3813702144362</v>
+        <v>78.58413015865221</v>
       </c>
       <c r="D55">
-        <v>196.5183702144362</v>
+        <v>196.1501301586522</v>
       </c>
       <c r="E55">
-        <v>-2.162999999999982</v>
+        <v>0.2660000000000196</v>
       </c>
       <c r="F55">
-        <v>128.737</v>
+        <v>131.166</v>
       </c>
       <c r="G55">
         <v>13.6</v>
@@ -5785,28 +5785,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M55">
-        <v>9.758264600000002</v>
+        <v>9.942382800000003</v>
       </c>
       <c r="N55">
-        <v>12.96840206666666</v>
+        <v>12.78428386666666</v>
       </c>
       <c r="O55">
-        <v>2.593680413333333</v>
+        <v>2.556856773333333</v>
       </c>
       <c r="P55">
-        <v>10.37472165333333</v>
+        <v>10.22742709333333</v>
       </c>
       <c r="Q55">
-        <v>15.11472165333333</v>
+        <v>14.96742709333333</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09637926587135937</v>
+        <v>0.09736320256762158</v>
       </c>
       <c r="T55">
-        <v>0.9594699833846412</v>
+        <v>0.9781348989256321</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.328966019907542</v>
+        <v>2.285837019538884</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07753267318110593</v>
+        <v>0.07762789140267295</v>
       </c>
       <c r="C56">
-        <v>78.58413015865221</v>
+        <v>75.78826755294975</v>
       </c>
       <c r="D56">
-        <v>196.1501301586522</v>
+        <v>195.7832675529498</v>
       </c>
       <c r="E56">
-        <v>0.2660000000000196</v>
+        <v>2.695000000000022</v>
       </c>
       <c r="F56">
-        <v>131.166</v>
+        <v>133.595</v>
       </c>
       <c r="G56">
         <v>13.6</v>
@@ -5867,28 +5867,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M56">
-        <v>9.942382800000003</v>
+        <v>10.126501</v>
       </c>
       <c r="N56">
-        <v>12.78428386666666</v>
+        <v>12.60016566666666</v>
       </c>
       <c r="O56">
-        <v>2.556856773333333</v>
+        <v>2.520033133333333</v>
       </c>
       <c r="P56">
-        <v>10.22742709333333</v>
+        <v>10.08013253333333</v>
       </c>
       <c r="Q56">
-        <v>14.96742709333333</v>
+        <v>14.82013253333333</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09736320256762158</v>
+        <v>0.09839086978371768</v>
       </c>
       <c r="T56">
-        <v>0.9781348989256321</v>
+        <v>0.997629366268445</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.285837019538884</v>
+        <v>2.244276346456358</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07762789140267295</v>
+        <v>0.07772310962423998</v>
       </c>
       <c r="C57">
-        <v>75.78826755294975</v>
+        <v>72.9937746829589</v>
       </c>
       <c r="D57">
-        <v>195.7832675529498</v>
+        <v>195.4177746829589</v>
       </c>
       <c r="E57">
-        <v>2.695000000000022</v>
+        <v>5.124000000000024</v>
       </c>
       <c r="F57">
-        <v>133.595</v>
+        <v>136.024</v>
       </c>
       <c r="G57">
         <v>13.6</v>
@@ -5949,28 +5949,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M57">
-        <v>10.126501</v>
+        <v>10.3106192</v>
       </c>
       <c r="N57">
-        <v>12.60016566666666</v>
+        <v>12.41604746666666</v>
       </c>
       <c r="O57">
-        <v>2.520033133333333</v>
+        <v>2.483209493333333</v>
       </c>
       <c r="P57">
-        <v>10.08013253333333</v>
+        <v>9.932837973333331</v>
       </c>
       <c r="Q57">
-        <v>14.82013253333333</v>
+        <v>14.67283797333333</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09839086978371768</v>
+        <v>0.09946524914599997</v>
       </c>
       <c r="T57">
-        <v>0.997629366268445</v>
+        <v>1.018009945763204</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.244276346456358</v>
+        <v>2.20419998312678</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07772310962423998</v>
+        <v>0.077818327845807</v>
       </c>
       <c r="C58">
-        <v>72.9937746829589</v>
+        <v>70.20064389180786</v>
       </c>
       <c r="D58">
-        <v>195.4177746829589</v>
+        <v>195.0536438918079</v>
       </c>
       <c r="E58">
-        <v>5.124000000000024</v>
+        <v>7.553000000000026</v>
       </c>
       <c r="F58">
-        <v>136.024</v>
+        <v>138.453</v>
       </c>
       <c r="G58">
         <v>13.6</v>
@@ -6031,28 +6031,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M58">
-        <v>10.3106192</v>
+        <v>10.4947374</v>
       </c>
       <c r="N58">
-        <v>12.41604746666666</v>
+        <v>12.23192926666666</v>
       </c>
       <c r="O58">
-        <v>2.483209493333333</v>
+        <v>2.446385853333333</v>
       </c>
       <c r="P58">
-        <v>9.932837973333331</v>
+        <v>9.785543413333331</v>
       </c>
       <c r="Q58">
-        <v>14.67283797333333</v>
+        <v>14.52554341333333</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09946524914599997</v>
+        <v>0.1005895996414116</v>
       </c>
       <c r="T58">
-        <v>1.018009945763204</v>
+        <v>1.039338459187952</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.20419998312678</v>
+        <v>2.165529807984205</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.077818327845807</v>
+        <v>0.07791354606737405</v>
       </c>
       <c r="C59">
-        <v>70.20064389180786</v>
+        <v>67.40886757958816</v>
       </c>
       <c r="D59">
-        <v>195.0536438918079</v>
+        <v>194.6908675795882</v>
       </c>
       <c r="E59">
-        <v>7.553000000000026</v>
+        <v>9.982000000000028</v>
       </c>
       <c r="F59">
-        <v>138.453</v>
+        <v>140.882</v>
       </c>
       <c r="G59">
         <v>13.6</v>
@@ -6113,28 +6113,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M59">
-        <v>10.4947374</v>
+        <v>10.6788556</v>
       </c>
       <c r="N59">
-        <v>12.23192926666666</v>
+        <v>12.04781106666666</v>
       </c>
       <c r="O59">
-        <v>2.446385853333333</v>
+        <v>2.409562213333333</v>
       </c>
       <c r="P59">
-        <v>9.785543413333331</v>
+        <v>9.63824885333333</v>
       </c>
       <c r="Q59">
-        <v>14.52554341333333</v>
+        <v>14.37824885333333</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1005895996414116</v>
+        <v>0.1017674906366049</v>
       </c>
       <c r="T59">
-        <v>1.039338459187952</v>
+        <v>1.061682616109116</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.165529807984205</v>
+        <v>2.128193087156891</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07791354606737404</v>
+        <v>0.07800876428894106</v>
       </c>
       <c r="C60">
-        <v>67.40886757958825</v>
+        <v>64.6184382028265</v>
       </c>
       <c r="D60">
-        <v>194.6908675795883</v>
+        <v>194.3294382028265</v>
       </c>
       <c r="E60">
-        <v>9.981999999999999</v>
+        <v>12.411</v>
       </c>
       <c r="F60">
-        <v>140.882</v>
+        <v>143.311</v>
       </c>
       <c r="G60">
         <v>13.6</v>
@@ -6195,28 +6195,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M60">
-        <v>10.6788556</v>
+        <v>10.8629738</v>
       </c>
       <c r="N60">
-        <v>12.04781106666666</v>
+        <v>11.86369286666667</v>
       </c>
       <c r="O60">
-        <v>2.409562213333333</v>
+        <v>2.372738573333333</v>
       </c>
       <c r="P60">
-        <v>9.638248853333332</v>
+        <v>9.490954293333333</v>
       </c>
       <c r="Q60">
-        <v>14.37824885333333</v>
+        <v>14.23095429333333</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1017674906366048</v>
+        <v>0.1030028397291245</v>
       </c>
       <c r="T60">
-        <v>1.061682616109115</v>
+        <v>1.085116731904483</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.128193087156892</v>
+        <v>2.092122017883046</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07800876428894106</v>
+        <v>0.0781039825105081</v>
       </c>
       <c r="C61">
-        <v>64.6184382028265</v>
+        <v>61.82934827396073</v>
       </c>
       <c r="D61">
-        <v>194.3294382028265</v>
+        <v>193.9693482739607</v>
       </c>
       <c r="E61">
-        <v>12.411</v>
+        <v>14.84</v>
       </c>
       <c r="F61">
-        <v>143.311</v>
+        <v>145.74</v>
       </c>
       <c r="G61">
         <v>13.6</v>
@@ -6277,28 +6277,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M61">
-        <v>10.8629738</v>
+        <v>11.047092</v>
       </c>
       <c r="N61">
-        <v>11.86369286666667</v>
+        <v>11.67957466666667</v>
       </c>
       <c r="O61">
-        <v>2.372738573333333</v>
+        <v>2.335914933333333</v>
       </c>
       <c r="P61">
-        <v>9.490954293333333</v>
+        <v>9.343659733333332</v>
       </c>
       <c r="Q61">
-        <v>14.23095429333333</v>
+        <v>14.08365973333333</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1030028397291245</v>
+        <v>0.1042999562762702</v>
       </c>
       <c r="T61">
-        <v>1.085116731904483</v>
+        <v>1.109722553489618</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.092122017883046</v>
+        <v>2.057253317584996</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.0781039825105081</v>
+        <v>0.07819920073207512</v>
       </c>
       <c r="C62">
-        <v>61.82934827396073</v>
+        <v>59.04159036082399</v>
       </c>
       <c r="D62">
-        <v>193.9693482739607</v>
+        <v>193.610590360824</v>
       </c>
       <c r="E62">
-        <v>14.84</v>
+        <v>17.26900000000001</v>
       </c>
       <c r="F62">
-        <v>145.74</v>
+        <v>148.169</v>
       </c>
       <c r="G62">
         <v>13.6</v>
@@ -6359,28 +6359,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M62">
-        <v>11.047092</v>
+        <v>11.2312102</v>
       </c>
       <c r="N62">
-        <v>11.67957466666667</v>
+        <v>11.49545646666667</v>
       </c>
       <c r="O62">
-        <v>2.335914933333333</v>
+        <v>2.299091293333333</v>
       </c>
       <c r="P62">
-        <v>9.343659733333332</v>
+        <v>9.196365173333332</v>
       </c>
       <c r="Q62">
-        <v>14.08365973333333</v>
+        <v>13.93636517333333</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1042999562762702</v>
+        <v>0.1056635916207054</v>
       </c>
       <c r="T62">
-        <v>1.109722553489618</v>
+        <v>1.13559021207912</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.057253317584996</v>
+        <v>2.023527853362291</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07819920073207512</v>
+        <v>0.08533761895364214</v>
       </c>
       <c r="C63">
-        <v>59.04159036082399</v>
+        <v>33.03575784175473</v>
       </c>
       <c r="D63">
-        <v>193.610590360824</v>
+        <v>170.0337578417547</v>
       </c>
       <c r="E63">
-        <v>17.26900000000001</v>
+        <v>19.69800000000001</v>
       </c>
       <c r="F63">
-        <v>148.169</v>
+        <v>150.598</v>
       </c>
       <c r="G63">
         <v>13.6</v>
@@ -6441,45 +6441,45 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M63">
-        <v>11.2312102</v>
+        <v>13.55382</v>
       </c>
       <c r="N63">
-        <v>11.49545646666667</v>
+        <v>9.172846666666667</v>
       </c>
       <c r="O63">
-        <v>2.299091293333333</v>
+        <v>1.834569333333333</v>
       </c>
       <c r="P63">
-        <v>9.196365173333332</v>
+        <v>7.338277333333333</v>
       </c>
       <c r="Q63">
-        <v>13.93636517333333</v>
+        <v>12.07827733333333</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1056635916207054</v>
+        <v>0.1070989972464267</v>
       </c>
       <c r="T63">
-        <v>1.13559021207912</v>
+        <v>1.162819326383858</v>
       </c>
       <c r="U63">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V63">
         <v>0.2</v>
       </c>
       <c r="W63">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.023527853362291</v>
+        <v>1.676772058848846</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08533761895364214</v>
+        <v>0.08554643717520916</v>
       </c>
       <c r="C64">
-        <v>33.03575784175473</v>
+        <v>30.00320736718729</v>
       </c>
       <c r="D64">
-        <v>170.0337578417547</v>
+        <v>169.4302073671873</v>
       </c>
       <c r="E64">
-        <v>19.69800000000001</v>
+        <v>22.12700000000001</v>
       </c>
       <c r="F64">
-        <v>150.598</v>
+        <v>153.027</v>
       </c>
       <c r="G64">
         <v>13.6</v>
@@ -6523,28 +6523,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M64">
-        <v>13.55382</v>
+        <v>13.77243</v>
       </c>
       <c r="N64">
-        <v>9.172846666666667</v>
+        <v>8.954236666666665</v>
       </c>
       <c r="O64">
-        <v>1.834569333333333</v>
+        <v>1.790847333333333</v>
       </c>
       <c r="P64">
-        <v>7.338277333333333</v>
+        <v>7.163389333333332</v>
       </c>
       <c r="Q64">
-        <v>12.07827733333333</v>
+        <v>11.90338933333333</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1070989972464267</v>
+        <v>0.1086119923654302</v>
       </c>
       <c r="T64">
-        <v>1.162819326383858</v>
+        <v>1.191520284705069</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.676772058848846</v>
+        <v>1.650156629343309</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08554643717520916</v>
+        <v>0.0857552553967762</v>
       </c>
       <c r="C65">
-        <v>30.00320736718729</v>
+        <v>26.97492645335004</v>
       </c>
       <c r="D65">
-        <v>169.4302073671873</v>
+        <v>168.8309264533501</v>
       </c>
       <c r="E65">
-        <v>22.12700000000001</v>
+        <v>24.55600000000001</v>
       </c>
       <c r="F65">
-        <v>153.027</v>
+        <v>155.456</v>
       </c>
       <c r="G65">
         <v>13.6</v>
@@ -6605,28 +6605,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M65">
-        <v>13.77243</v>
+        <v>13.99104</v>
       </c>
       <c r="N65">
-        <v>8.954236666666665</v>
+        <v>8.735626666666665</v>
       </c>
       <c r="O65">
-        <v>1.790847333333333</v>
+        <v>1.747125333333333</v>
       </c>
       <c r="P65">
-        <v>7.163389333333332</v>
+        <v>6.988501333333332</v>
       </c>
       <c r="Q65">
-        <v>11.90338933333333</v>
+        <v>11.72850133333333</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1086119923654302</v>
+        <v>0.1102090427688228</v>
       </c>
       <c r="T65">
-        <v>1.191520284705069</v>
+        <v>1.221815740710792</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.650156629343309</v>
+        <v>1.624372932009819</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0857552553967762</v>
+        <v>0.08596407361834323</v>
       </c>
       <c r="C66">
-        <v>26.97492645335004</v>
+        <v>23.95086995514001</v>
       </c>
       <c r="D66">
-        <v>168.8309264533501</v>
+        <v>168.23586995514</v>
       </c>
       <c r="E66">
-        <v>24.55600000000001</v>
+        <v>26.98500000000001</v>
       </c>
       <c r="F66">
-        <v>155.456</v>
+        <v>157.885</v>
       </c>
       <c r="G66">
         <v>13.6</v>
@@ -6687,28 +6687,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M66">
-        <v>13.99104</v>
+        <v>14.20965</v>
       </c>
       <c r="N66">
-        <v>8.735626666666665</v>
+        <v>8.517016666666665</v>
       </c>
       <c r="O66">
-        <v>1.747125333333333</v>
+        <v>1.703403333333333</v>
       </c>
       <c r="P66">
-        <v>6.988501333333332</v>
+        <v>6.813613333333332</v>
       </c>
       <c r="Q66">
-        <v>11.72850133333333</v>
+        <v>11.55361333333333</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1102090427688228</v>
+        <v>0.1118973531952664</v>
       </c>
       <c r="T66">
-        <v>1.221815740710792</v>
+        <v>1.253842365631127</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.624372932009819</v>
+        <v>1.599382579209668</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08596407361834323</v>
+        <v>0.08617289183991025</v>
       </c>
       <c r="C67">
-        <v>23.95086995514001</v>
+        <v>20.93099336168714</v>
       </c>
       <c r="D67">
-        <v>168.23586995514</v>
+        <v>167.6449933616872</v>
       </c>
       <c r="E67">
-        <v>26.98500000000001</v>
+        <v>29.41400000000002</v>
       </c>
       <c r="F67">
-        <v>157.885</v>
+        <v>160.314</v>
       </c>
       <c r="G67">
         <v>13.6</v>
@@ -6769,28 +6769,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M67">
-        <v>14.20965</v>
+        <v>14.42826</v>
       </c>
       <c r="N67">
-        <v>8.517016666666665</v>
+        <v>8.298406666666665</v>
       </c>
       <c r="O67">
-        <v>1.703403333333333</v>
+        <v>1.659681333333333</v>
       </c>
       <c r="P67">
-        <v>6.813613333333332</v>
+        <v>6.638725333333332</v>
       </c>
       <c r="Q67">
-        <v>11.55361333333333</v>
+        <v>11.37872533333333</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1118973531952664</v>
+        <v>0.113684975999736</v>
       </c>
       <c r="T67">
-        <v>1.253842365631127</v>
+        <v>1.287752909664424</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.599382579209668</v>
+        <v>1.575149509827704</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08617289183991025</v>
+        <v>0.08638171006147727</v>
       </c>
       <c r="C68">
-        <v>20.93099336168714</v>
+        <v>17.91525278525566</v>
       </c>
       <c r="D68">
-        <v>167.6449933616872</v>
+        <v>167.0582527852557</v>
       </c>
       <c r="E68">
-        <v>29.41400000000002</v>
+        <v>31.84300000000002</v>
       </c>
       <c r="F68">
-        <v>160.314</v>
+        <v>162.743</v>
       </c>
       <c r="G68">
         <v>13.6</v>
@@ -6851,28 +6851,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M68">
-        <v>14.42826</v>
+        <v>14.64687</v>
       </c>
       <c r="N68">
-        <v>8.298406666666665</v>
+        <v>8.079796666666665</v>
       </c>
       <c r="O68">
-        <v>1.659681333333333</v>
+        <v>1.615959333333333</v>
       </c>
       <c r="P68">
-        <v>6.638725333333332</v>
+        <v>6.463837333333332</v>
       </c>
       <c r="Q68">
-        <v>11.37872533333333</v>
+        <v>11.20383733333333</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.113684975999736</v>
+        <v>0.1155809395802342</v>
       </c>
       <c r="T68">
-        <v>1.287752909664424</v>
+        <v>1.323718638184586</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.575149509827704</v>
+        <v>1.551639815651171</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08638171006147727</v>
+        <v>0.0865905282830443</v>
       </c>
       <c r="C69">
-        <v>17.91525278525566</v>
+        <v>14.90360495037734</v>
       </c>
       <c r="D69">
-        <v>167.0582527852557</v>
+        <v>166.4756049503774</v>
       </c>
       <c r="E69">
-        <v>31.84300000000002</v>
+        <v>34.27200000000002</v>
       </c>
       <c r="F69">
-        <v>162.743</v>
+        <v>165.172</v>
       </c>
       <c r="G69">
         <v>13.6</v>
@@ -6933,28 +6933,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M69">
-        <v>14.64687</v>
+        <v>14.86548</v>
       </c>
       <c r="N69">
-        <v>8.079796666666665</v>
+        <v>7.861186666666665</v>
       </c>
       <c r="O69">
-        <v>1.615959333333333</v>
+        <v>1.572237333333333</v>
       </c>
       <c r="P69">
-        <v>6.463837333333332</v>
+        <v>6.288949333333332</v>
       </c>
       <c r="Q69">
-        <v>11.20383733333333</v>
+        <v>11.02894933333333</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1155809395802342</v>
+        <v>0.1175954008845135</v>
       </c>
       <c r="T69">
-        <v>1.323718638184586</v>
+        <v>1.361932224737259</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.551639815651171</v>
+        <v>1.528821583068065</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.0865905282830443</v>
+        <v>0.08679934650461132</v>
       </c>
       <c r="C70">
-        <v>14.90360495037734</v>
+        <v>11.89600718321202</v>
       </c>
       <c r="D70">
-        <v>166.4756049503774</v>
+        <v>165.8970071832121</v>
       </c>
       <c r="E70">
-        <v>34.27200000000002</v>
+        <v>36.70100000000002</v>
       </c>
       <c r="F70">
-        <v>165.172</v>
+        <v>167.601</v>
       </c>
       <c r="G70">
         <v>13.6</v>
@@ -7015,28 +7015,28 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M70">
-        <v>14.86548</v>
+        <v>15.08409</v>
       </c>
       <c r="N70">
-        <v>7.861186666666665</v>
+        <v>7.642576666666665</v>
       </c>
       <c r="O70">
-        <v>1.572237333333333</v>
+        <v>1.528515333333333</v>
       </c>
       <c r="P70">
-        <v>6.288949333333332</v>
+        <v>6.114061333333332</v>
       </c>
       <c r="Q70">
-        <v>11.02894933333333</v>
+        <v>10.85406133333333</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1175954008845135</v>
+        <v>0.1197398274342301</v>
       </c>
       <c r="T70">
-        <v>1.361932224737259</v>
+        <v>1.40261120397075</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.528821583068065</v>
+        <v>1.506664748530847</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08679934650461132</v>
+        <v>0.1209885397546588</v>
       </c>
       <c r="C71">
-        <v>11.89600718321202</v>
+        <v>-50.69880226505902</v>
       </c>
       <c r="D71">
-        <v>165.8970071832121</v>
+        <v>105.731197734941</v>
       </c>
       <c r="E71">
-        <v>36.70100000000002</v>
+        <v>39.13000000000002</v>
       </c>
       <c r="F71">
-        <v>167.601</v>
+        <v>170.03</v>
       </c>
       <c r="G71">
         <v>13.6</v>
@@ -7097,45 +7097,45 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M71">
-        <v>15.08409</v>
+        <v>24.96040400000001</v>
       </c>
       <c r="N71">
-        <v>7.642576666666665</v>
+        <v>-2.233737333333341</v>
       </c>
       <c r="O71">
-        <v>1.528515333333333</v>
+        <v>-0.4467474666666682</v>
       </c>
       <c r="P71">
-        <v>6.114061333333332</v>
+        <v>-1.786989866666673</v>
       </c>
       <c r="Q71">
-        <v>10.85406133333333</v>
+        <v>2.953010133333327</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1197398274342301</v>
+        <v>0.1231377197713729</v>
       </c>
       <c r="T71">
-        <v>1.40261120397075</v>
+        <v>1.46706796600745</v>
       </c>
       <c r="U71">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.2</v>
+        <v>0.1821017533743978</v>
       </c>
       <c r="W71">
-        <v>0.07199999999999999</v>
+        <v>0.1200674626046384</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y71">
-        <v>1.506664748530847</v>
+        <v>0.9105087668719889</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1209885397546588</v>
+        <v>0.1219985397546588</v>
       </c>
       <c r="C72">
-        <v>-50.69880226505902</v>
+        <v>-54.24857791722754</v>
       </c>
       <c r="D72">
-        <v>105.731197734941</v>
+        <v>104.6104220827725</v>
       </c>
       <c r="E72">
-        <v>39.13000000000002</v>
+        <v>41.55900000000003</v>
       </c>
       <c r="F72">
-        <v>170.03</v>
+        <v>172.459</v>
       </c>
       <c r="G72">
         <v>13.6</v>
@@ -7179,37 +7179,37 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M72">
-        <v>24.96040400000001</v>
+        <v>25.31698120000001</v>
       </c>
       <c r="N72">
-        <v>-2.233737333333341</v>
+        <v>-2.590314533333341</v>
       </c>
       <c r="O72">
-        <v>-0.4467474666666682</v>
+        <v>-0.5180629066666683</v>
       </c>
       <c r="P72">
-        <v>-1.786989866666673</v>
+        <v>-2.072251626666673</v>
       </c>
       <c r="Q72">
-        <v>2.953010133333327</v>
+        <v>2.667748373333327</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1231377197713729</v>
+        <v>0.1258045376945237</v>
       </c>
       <c r="T72">
-        <v>1.46706796600745</v>
+        <v>1.517656516559431</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.1821017533743978</v>
+        <v>0.1795369399465894</v>
       </c>
       <c r="W72">
-        <v>0.1200674626046384</v>
+        <v>0.1204439772158407</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.9105087668719889</v>
+        <v>0.8976846997329468</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1219985397546588</v>
+        <v>0.1230085397546588</v>
       </c>
       <c r="C73">
-        <v>-54.24857791722751</v>
+        <v>-57.77484182651146</v>
       </c>
       <c r="D73">
-        <v>104.6104220827725</v>
+        <v>103.5131581734885</v>
       </c>
       <c r="E73">
-        <v>41.559</v>
+        <v>43.988</v>
       </c>
       <c r="F73">
-        <v>172.459</v>
+        <v>174.888</v>
       </c>
       <c r="G73">
         <v>13.6</v>
@@ -7261,37 +7261,37 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M73">
-        <v>25.3169812</v>
+        <v>25.6735584</v>
       </c>
       <c r="N73">
-        <v>-2.590314533333338</v>
+        <v>-2.946891733333338</v>
       </c>
       <c r="O73">
-        <v>-0.5180629066666675</v>
+        <v>-0.5893783466666677</v>
       </c>
       <c r="P73">
-        <v>-2.07225162666667</v>
+        <v>-2.35751338666667</v>
       </c>
       <c r="Q73">
-        <v>2.66774837333333</v>
+        <v>2.38248661333333</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1258045376945237</v>
+        <v>0.1286618426121853</v>
       </c>
       <c r="T73">
-        <v>1.517656516559431</v>
+        <v>1.571858535007982</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.1795369399465894</v>
+        <v>0.1770433713362201</v>
       </c>
       <c r="W73">
-        <v>0.1204439772158407</v>
+        <v>0.1208100330878429</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.897684699732947</v>
+        <v>0.8852168566811005</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1230085397546588</v>
+        <v>0.1240185397546588</v>
       </c>
       <c r="C74">
-        <v>-57.77484182651146</v>
+        <v>-61.27832616068092</v>
       </c>
       <c r="D74">
-        <v>103.5131581734885</v>
+        <v>102.4386738393191</v>
       </c>
       <c r="E74">
-        <v>43.988</v>
+        <v>46.417</v>
       </c>
       <c r="F74">
-        <v>174.888</v>
+        <v>177.317</v>
       </c>
       <c r="G74">
         <v>13.6</v>
@@ -7343,37 +7343,37 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M74">
-        <v>25.6735584</v>
+        <v>26.0301356</v>
       </c>
       <c r="N74">
-        <v>-2.946891733333338</v>
+        <v>-3.303468933333338</v>
       </c>
       <c r="O74">
-        <v>-0.5893783466666677</v>
+        <v>-0.6606937866666677</v>
       </c>
       <c r="P74">
-        <v>-2.35751338666667</v>
+        <v>-2.642775146666671</v>
       </c>
       <c r="Q74">
-        <v>2.38248661333333</v>
+        <v>2.09722485333333</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1286618426121853</v>
+        <v>0.1317307997459699</v>
       </c>
       <c r="T74">
-        <v>1.571858535007982</v>
+        <v>1.630075517786055</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.1770433713362201</v>
+        <v>0.1746181196740801</v>
       </c>
       <c r="W74">
-        <v>0.1208100330878429</v>
+        <v>0.121166060031845</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8852168566811005</v>
+        <v>0.8730905983704005</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1240185397546588</v>
+        <v>0.1250285397546588</v>
       </c>
       <c r="C75">
-        <v>-61.27832616068092</v>
+        <v>-64.75973299971436</v>
       </c>
       <c r="D75">
-        <v>102.4386738393191</v>
+        <v>101.3862670002857</v>
       </c>
       <c r="E75">
-        <v>46.417</v>
+        <v>48.846</v>
       </c>
       <c r="F75">
-        <v>177.317</v>
+        <v>179.746</v>
       </c>
       <c r="G75">
         <v>13.6</v>
@@ -7425,37 +7425,37 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M75">
-        <v>26.0301356</v>
+        <v>26.38671280000001</v>
       </c>
       <c r="N75">
-        <v>-3.303468933333338</v>
+        <v>-3.660046133333339</v>
       </c>
       <c r="O75">
-        <v>-0.6606937866666677</v>
+        <v>-0.7320092266666678</v>
       </c>
       <c r="P75">
-        <v>-2.642775146666671</v>
+        <v>-2.928036906666671</v>
       </c>
       <c r="Q75">
-        <v>2.09722485333333</v>
+        <v>1.811963093333329</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1317307997459699</v>
+        <v>0.1350358305054303</v>
       </c>
       <c r="T75">
-        <v>1.630075517786055</v>
+        <v>1.692770730008596</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.1746181196740801</v>
+        <v>0.1722584153541601</v>
       </c>
       <c r="W75">
-        <v>0.121166060031845</v>
+        <v>0.1215124646260093</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8730905983704005</v>
+        <v>0.8612920767708004</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1250285397546588</v>
+        <v>0.1260385397546588</v>
       </c>
       <c r="C76">
-        <v>-64.75973299971436</v>
+        <v>-68.21973586562112</v>
       </c>
       <c r="D76">
-        <v>101.3862670002857</v>
+        <v>100.3552641343789</v>
       </c>
       <c r="E76">
-        <v>48.846</v>
+        <v>51.27500000000001</v>
       </c>
       <c r="F76">
-        <v>179.746</v>
+        <v>182.175</v>
       </c>
       <c r="G76">
         <v>13.6</v>
@@ -7507,37 +7507,37 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M76">
-        <v>26.38671280000001</v>
+        <v>26.74329000000001</v>
       </c>
       <c r="N76">
-        <v>-3.660046133333339</v>
+        <v>-4.016623333333339</v>
       </c>
       <c r="O76">
-        <v>-0.7320092266666678</v>
+        <v>-0.8033246666666678</v>
       </c>
       <c r="P76">
-        <v>-2.928036906666671</v>
+        <v>-3.213298666666671</v>
       </c>
       <c r="Q76">
-        <v>1.811963093333329</v>
+        <v>1.526701333333329</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1350358305054303</v>
+        <v>0.1386052637256475</v>
       </c>
       <c r="T76">
-        <v>1.692770730008596</v>
+        <v>1.76048155920894</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.1722584153541601</v>
+        <v>0.1699616364827713</v>
       </c>
       <c r="W76">
-        <v>0.1215124646260093</v>
+        <v>0.1218496317643292</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8612920767708004</v>
+        <v>0.8498081824138564</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1260385397546588</v>
+        <v>0.1270485397546588</v>
       </c>
       <c r="C77">
-        <v>-68.21973586562112</v>
+        <v>-71.65898115986259</v>
       </c>
       <c r="D77">
-        <v>100.3552641343789</v>
+        <v>99.34501884013743</v>
       </c>
       <c r="E77">
-        <v>51.27500000000001</v>
+        <v>53.70400000000001</v>
       </c>
       <c r="F77">
-        <v>182.175</v>
+        <v>184.604</v>
       </c>
       <c r="G77">
         <v>13.6</v>
@@ -7589,37 +7589,37 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M77">
-        <v>26.74329000000001</v>
+        <v>27.09986720000001</v>
       </c>
       <c r="N77">
-        <v>-4.016623333333339</v>
+        <v>-4.373200533333339</v>
       </c>
       <c r="O77">
-        <v>-0.8033246666666678</v>
+        <v>-0.8746401066666678</v>
       </c>
       <c r="P77">
-        <v>-3.213298666666671</v>
+        <v>-3.498560426666671</v>
       </c>
       <c r="Q77">
-        <v>1.526701333333329</v>
+        <v>1.241439573333329</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1386052637256475</v>
+        <v>0.1424721497142162</v>
       </c>
       <c r="T77">
-        <v>1.76048155920894</v>
+        <v>1.833834957509313</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1699616364827713</v>
+        <v>0.1677252991606296</v>
       </c>
       <c r="W77">
-        <v>0.1218496317643292</v>
+        <v>0.1221779260832196</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8498081824138564</v>
+        <v>0.8386264958031477</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1270485397546588</v>
+        <v>0.1280585397546588</v>
       </c>
       <c r="C78">
-        <v>-71.65898115986259</v>
+        <v>-75.07808951481785</v>
       </c>
       <c r="D78">
-        <v>99.34501884013743</v>
+        <v>98.35491048518217</v>
       </c>
       <c r="E78">
-        <v>53.70400000000001</v>
+        <v>56.13300000000001</v>
       </c>
       <c r="F78">
-        <v>184.604</v>
+        <v>187.033</v>
       </c>
       <c r="G78">
         <v>13.6</v>
@@ -7671,37 +7671,37 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M78">
-        <v>27.09986720000001</v>
+        <v>27.45644440000001</v>
       </c>
       <c r="N78">
-        <v>-4.373200533333339</v>
+        <v>-4.729777733333339</v>
       </c>
       <c r="O78">
-        <v>-0.8746401066666678</v>
+        <v>-0.9459555466666679</v>
       </c>
       <c r="P78">
-        <v>-3.498560426666671</v>
+        <v>-3.783822186666671</v>
       </c>
       <c r="Q78">
-        <v>1.241439573333329</v>
+        <v>0.956177813333329</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1424721497142162</v>
+        <v>0.1466752866583125</v>
       </c>
       <c r="T78">
-        <v>1.833834957509313</v>
+        <v>1.913566912183631</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1677252991606296</v>
+        <v>0.1655470485221798</v>
       </c>
       <c r="W78">
-        <v>0.1221779260832196</v>
+        <v>0.122497693276944</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8386264958031477</v>
+        <v>0.827735242610899</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1280585397546588</v>
+        <v>0.1290685397546588</v>
       </c>
       <c r="C79">
-        <v>-75.07808951481785</v>
+        <v>-78.47765706523224</v>
       </c>
       <c r="D79">
-        <v>98.35491048518217</v>
+        <v>97.38434293476779</v>
       </c>
       <c r="E79">
-        <v>56.13300000000001</v>
+        <v>58.56200000000001</v>
       </c>
       <c r="F79">
-        <v>187.033</v>
+        <v>189.462</v>
       </c>
       <c r="G79">
         <v>13.6</v>
@@ -7753,37 +7753,37 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M79">
-        <v>27.45644440000001</v>
+        <v>27.81302160000001</v>
       </c>
       <c r="N79">
-        <v>-4.729777733333339</v>
+        <v>-5.08635493333334</v>
       </c>
       <c r="O79">
-        <v>-0.9459555466666679</v>
+        <v>-1.017270986666668</v>
       </c>
       <c r="P79">
-        <v>-3.783822186666671</v>
+        <v>-4.069083946666671</v>
       </c>
       <c r="Q79">
-        <v>0.956177813333329</v>
+        <v>0.6709160533333289</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1466752866583125</v>
+        <v>0.1512605269609631</v>
       </c>
       <c r="T79">
-        <v>1.913566912183631</v>
+        <v>2.000547226373795</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1655470485221798</v>
+        <v>0.1634246504642032</v>
       </c>
       <c r="W79">
-        <v>0.122497693276944</v>
+        <v>0.122809261311855</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.827735242610899</v>
+        <v>0.8171232523210158</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1290685397546588</v>
+        <v>0.1300785397546588</v>
       </c>
       <c r="C80">
-        <v>-78.47765706523224</v>
+        <v>-81.8582566451209</v>
       </c>
       <c r="D80">
-        <v>97.38434293476779</v>
+        <v>96.43274335487912</v>
       </c>
       <c r="E80">
-        <v>58.56200000000001</v>
+        <v>60.99100000000001</v>
       </c>
       <c r="F80">
-        <v>189.462</v>
+        <v>191.891</v>
       </c>
       <c r="G80">
         <v>13.6</v>
@@ -7835,37 +7835,37 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M80">
-        <v>27.81302160000001</v>
+        <v>28.16959880000001</v>
       </c>
       <c r="N80">
-        <v>-5.08635493333334</v>
+        <v>-5.44293213333334</v>
       </c>
       <c r="O80">
-        <v>-1.017270986666668</v>
+        <v>-1.088586426666668</v>
       </c>
       <c r="P80">
-        <v>-4.069083946666671</v>
+        <v>-4.354345706666672</v>
       </c>
       <c r="Q80">
-        <v>0.6709160533333289</v>
+        <v>0.385654293333328</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1512605269609631</v>
+        <v>0.156282456816247</v>
       </c>
       <c r="T80">
-        <v>2.000547226373795</v>
+        <v>2.095811380010643</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1634246504642032</v>
+        <v>0.161355984002631</v>
       </c>
       <c r="W80">
-        <v>0.122809261311855</v>
+        <v>0.1231129415484138</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8171232523210158</v>
+        <v>0.8067799200131548</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1300785397546588</v>
+        <v>0.1752000783870991</v>
       </c>
       <c r="C81">
-        <v>-81.8582566451209</v>
+        <v>-113.5916907350215</v>
       </c>
       <c r="D81">
-        <v>96.43274335487912</v>
+        <v>67.12830926497854</v>
       </c>
       <c r="E81">
-        <v>60.99100000000001</v>
+        <v>63.42000000000002</v>
       </c>
       <c r="F81">
-        <v>191.891</v>
+        <v>194.32</v>
       </c>
       <c r="G81">
         <v>13.6</v>
@@ -7917,45 +7917,45 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M81">
-        <v>28.16959880000001</v>
+        <v>39.01945600000001</v>
       </c>
       <c r="N81">
-        <v>-5.44293213333334</v>
+        <v>-16.29278933333334</v>
       </c>
       <c r="O81">
-        <v>-1.088586426666668</v>
+        <v>-3.258557866666668</v>
       </c>
       <c r="P81">
-        <v>-4.354345706666672</v>
+        <v>-13.03423146666667</v>
       </c>
       <c r="Q81">
-        <v>0.385654293333328</v>
+        <v>-8.294231466666671</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.156282456816247</v>
+        <v>0.1663642728192613</v>
       </c>
       <c r="T81">
-        <v>2.095811380010643</v>
+        <v>2.287059704126327</v>
       </c>
       <c r="U81">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.161355984002631</v>
+        <v>0.1164888955226165</v>
       </c>
       <c r="W81">
-        <v>0.1231129415484138</v>
+        <v>0.1774090297790586</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.8067799200131548</v>
+        <v>0.5824444776130826</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1752000783870991</v>
+        <v>0.1767500783870991</v>
       </c>
       <c r="C82">
-        <v>-113.5916907350215</v>
+        <v>-116.7141999670412</v>
       </c>
       <c r="D82">
-        <v>67.12830926497854</v>
+        <v>66.43480003295882</v>
       </c>
       <c r="E82">
-        <v>63.42000000000002</v>
+        <v>65.84900000000002</v>
       </c>
       <c r="F82">
-        <v>194.32</v>
+        <v>196.749</v>
       </c>
       <c r="G82">
         <v>13.6</v>
@@ -7999,37 +7999,37 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M82">
-        <v>39.01945600000001</v>
+        <v>39.50719920000001</v>
       </c>
       <c r="N82">
-        <v>-16.29278933333334</v>
+        <v>-16.78053253333334</v>
       </c>
       <c r="O82">
-        <v>-3.258557866666668</v>
+        <v>-3.356106506666669</v>
       </c>
       <c r="P82">
-        <v>-13.03423146666667</v>
+        <v>-13.42442602666667</v>
       </c>
       <c r="Q82">
-        <v>-8.294231466666671</v>
+        <v>-8.684426026666674</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1663642728192613</v>
+        <v>0.1727097608623803</v>
       </c>
       <c r="T82">
-        <v>2.287059704126327</v>
+        <v>2.407431267501397</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1164888955226165</v>
+        <v>0.1150507610099916</v>
       </c>
       <c r="W82">
-        <v>0.1774090297790586</v>
+        <v>0.1776978071891937</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5824444776130826</v>
+        <v>0.575253805049958</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1767500783870991</v>
+        <v>0.1783000783870992</v>
       </c>
       <c r="C83">
-        <v>-116.7141999670412</v>
+        <v>-119.8225262984677</v>
       </c>
       <c r="D83">
-        <v>66.43480003295882</v>
+        <v>65.7554737015323</v>
       </c>
       <c r="E83">
-        <v>65.84900000000002</v>
+        <v>68.27800000000002</v>
       </c>
       <c r="F83">
-        <v>196.749</v>
+        <v>199.178</v>
       </c>
       <c r="G83">
         <v>13.6</v>
@@ -8081,37 +8081,37 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M83">
-        <v>39.50719920000001</v>
+        <v>39.99494240000001</v>
       </c>
       <c r="N83">
-        <v>-16.78053253333334</v>
+        <v>-17.26827573333334</v>
       </c>
       <c r="O83">
-        <v>-3.356106506666669</v>
+        <v>-3.453655146666668</v>
       </c>
       <c r="P83">
-        <v>-13.42442602666667</v>
+        <v>-13.81462058666667</v>
       </c>
       <c r="Q83">
-        <v>-8.684426026666674</v>
+        <v>-9.074620586666672</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1727097608623803</v>
+        <v>0.1797603031325126</v>
       </c>
       <c r="T83">
-        <v>2.407431267501397</v>
+        <v>2.541177449029252</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1150507610099916</v>
+        <v>0.1136477029488942</v>
       </c>
       <c r="W83">
-        <v>0.1776978071891937</v>
+        <v>0.1779795412478621</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.575253805049958</v>
+        <v>0.5682385147444708</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1783000783870992</v>
+        <v>0.1798500783870992</v>
       </c>
       <c r="C84">
-        <v>-119.8225262984677</v>
+        <v>-122.9171004054501</v>
       </c>
       <c r="D84">
-        <v>65.7554737015323</v>
+        <v>65.08989959454998</v>
       </c>
       <c r="E84">
-        <v>68.27800000000002</v>
+        <v>70.70700000000002</v>
       </c>
       <c r="F84">
-        <v>199.178</v>
+        <v>201.607</v>
       </c>
       <c r="G84">
         <v>13.6</v>
@@ -8163,37 +8163,37 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M84">
-        <v>39.99494240000001</v>
+        <v>40.4826856</v>
       </c>
       <c r="N84">
-        <v>-17.26827573333334</v>
+        <v>-17.75601893333334</v>
       </c>
       <c r="O84">
-        <v>-3.453655146666668</v>
+        <v>-3.551203786666667</v>
       </c>
       <c r="P84">
-        <v>-13.81462058666667</v>
+        <v>-14.20481514666667</v>
       </c>
       <c r="Q84">
-        <v>-9.074620586666672</v>
+        <v>-9.46481514666667</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1797603031325126</v>
+        <v>0.1876403209638368</v>
       </c>
       <c r="T84">
-        <v>2.541177449029252</v>
+        <v>2.690658475442738</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1136477029488942</v>
+        <v>0.112278453515775</v>
       </c>
       <c r="W84">
-        <v>0.1779795412478621</v>
+        <v>0.1782544865340324</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5682385147444708</v>
+        <v>0.5613922675788749</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1798500783870992</v>
+        <v>0.1814000783870992</v>
       </c>
       <c r="C85">
-        <v>-122.9171004054501</v>
+        <v>-125.998335701724</v>
       </c>
       <c r="D85">
-        <v>65.08989959454998</v>
+        <v>64.43766429827603</v>
       </c>
       <c r="E85">
-        <v>70.70700000000002</v>
+        <v>73.13600000000002</v>
       </c>
       <c r="F85">
-        <v>201.607</v>
+        <v>204.036</v>
       </c>
       <c r="G85">
         <v>13.6</v>
@@ -8245,37 +8245,37 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M85">
-        <v>40.4826856</v>
+        <v>40.97042880000001</v>
       </c>
       <c r="N85">
-        <v>-17.75601893333334</v>
+        <v>-18.24376213333334</v>
       </c>
       <c r="O85">
-        <v>-3.551203786666667</v>
+        <v>-3.648752426666668</v>
       </c>
       <c r="P85">
-        <v>-14.20481514666667</v>
+        <v>-14.59500970666667</v>
       </c>
       <c r="Q85">
-        <v>-9.46481514666667</v>
+        <v>-9.855009706666673</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1876403209638368</v>
+        <v>0.1965053410240767</v>
       </c>
       <c r="T85">
-        <v>2.690658475442738</v>
+        <v>2.85882463015791</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.112278453515775</v>
+        <v>0.1109418052596348</v>
       </c>
       <c r="W85">
-        <v>0.1782544865340324</v>
+        <v>0.1785228855038653</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5613922675788749</v>
+        <v>0.554709026298174</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1814000783870991</v>
+        <v>0.1829500783870991</v>
       </c>
       <c r="C86">
-        <v>-125.9983357017239</v>
+        <v>-129.066629194924</v>
       </c>
       <c r="D86">
-        <v>64.43766429827606</v>
+        <v>63.79837080507595</v>
       </c>
       <c r="E86">
-        <v>73.136</v>
+        <v>75.565</v>
       </c>
       <c r="F86">
-        <v>204.036</v>
+        <v>206.465</v>
       </c>
       <c r="G86">
         <v>13.6</v>
@@ -8327,37 +8327,37 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M86">
-        <v>40.9704288</v>
+        <v>41.458172</v>
       </c>
       <c r="N86">
-        <v>-18.24376213333333</v>
+        <v>-18.73150533333334</v>
       </c>
       <c r="O86">
-        <v>-3.648752426666667</v>
+        <v>-3.746301066666668</v>
       </c>
       <c r="P86">
-        <v>-14.59500970666667</v>
+        <v>-14.98520426666667</v>
       </c>
       <c r="Q86">
-        <v>-9.855009706666667</v>
+        <v>-10.24520426666667</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1965053410240765</v>
+        <v>0.206552363759015</v>
       </c>
       <c r="T86">
-        <v>2.858824630157907</v>
+        <v>3.049412938835102</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1109418052596348</v>
+        <v>0.1096366075506979</v>
       </c>
       <c r="W86">
-        <v>0.1785228855038653</v>
+        <v>0.1787849692038199</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.554709026298174</v>
+        <v>0.5481830377534895</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1829500783870991</v>
+        <v>0.1845000783870991</v>
       </c>
       <c r="C87">
-        <v>-129.066629194924</v>
+        <v>-132.1223622924228</v>
       </c>
       <c r="D87">
-        <v>63.79837080507595</v>
+        <v>63.17163770757715</v>
       </c>
       <c r="E87">
-        <v>75.565</v>
+        <v>77.994</v>
       </c>
       <c r="F87">
-        <v>206.465</v>
+        <v>208.894</v>
       </c>
       <c r="G87">
         <v>13.6</v>
@@ -8409,37 +8409,37 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M87">
-        <v>41.458172</v>
+        <v>41.9459152</v>
       </c>
       <c r="N87">
-        <v>-18.73150533333334</v>
+        <v>-19.21924853333334</v>
       </c>
       <c r="O87">
-        <v>-3.746301066666668</v>
+        <v>-3.843849706666667</v>
       </c>
       <c r="P87">
-        <v>-14.98520426666667</v>
+        <v>-15.37539882666667</v>
       </c>
       <c r="Q87">
-        <v>-10.24520426666667</v>
+        <v>-10.63539882666667</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.206552363759015</v>
+        <v>0.2180346754560875</v>
       </c>
       <c r="T87">
-        <v>3.049412938835102</v>
+        <v>3.267228148751895</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1096366075506979</v>
+        <v>0.1083617632768526</v>
       </c>
       <c r="W87">
-        <v>0.1787849692038199</v>
+        <v>0.179040957934008</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5481830377534895</v>
+        <v>0.5418088163842629</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1845000783870991</v>
+        <v>0.1860500783870991</v>
       </c>
       <c r="C88">
-        <v>-132.1223622924228</v>
+        <v>-135.1659015601346</v>
       </c>
       <c r="D88">
-        <v>63.17163770757715</v>
+        <v>62.55709843986537</v>
       </c>
       <c r="E88">
-        <v>77.994</v>
+        <v>80.423</v>
       </c>
       <c r="F88">
-        <v>208.894</v>
+        <v>211.323</v>
       </c>
       <c r="G88">
         <v>13.6</v>
@@ -8491,37 +8491,37 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M88">
-        <v>41.9459152</v>
+        <v>42.43365840000001</v>
       </c>
       <c r="N88">
-        <v>-19.21924853333334</v>
+        <v>-19.70699173333334</v>
       </c>
       <c r="O88">
-        <v>-3.843849706666667</v>
+        <v>-3.941398346666668</v>
       </c>
       <c r="P88">
-        <v>-15.37539882666667</v>
+        <v>-15.76559338666667</v>
       </c>
       <c r="Q88">
-        <v>-10.63539882666667</v>
+        <v>-11.02559338666667</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2180346754560875</v>
+        <v>0.2312834966450173</v>
       </c>
       <c r="T88">
-        <v>3.267228148751895</v>
+        <v>3.518553390963579</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1083617632768526</v>
+        <v>0.1071162257679233</v>
       </c>
       <c r="W88">
-        <v>0.179040957934008</v>
+        <v>0.179291061865801</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5418088163842629</v>
+        <v>0.5355811288396162</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1860500783870991</v>
+        <v>0.1876000783870991</v>
       </c>
       <c r="C89">
-        <v>-135.1659015601346</v>
+        <v>-138.1975994374553</v>
       </c>
       <c r="D89">
-        <v>62.55709843986537</v>
+        <v>61.95440056254468</v>
       </c>
       <c r="E89">
-        <v>80.423</v>
+        <v>82.852</v>
       </c>
       <c r="F89">
-        <v>211.323</v>
+        <v>213.752</v>
       </c>
       <c r="G89">
         <v>13.6</v>
@@ -8573,37 +8573,37 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M89">
-        <v>42.43365840000001</v>
+        <v>42.9214016</v>
       </c>
       <c r="N89">
-        <v>-19.70699173333334</v>
+        <v>-20.19473493333334</v>
       </c>
       <c r="O89">
-        <v>-3.941398346666668</v>
+        <v>-4.038946986666668</v>
       </c>
       <c r="P89">
-        <v>-15.76559338666667</v>
+        <v>-16.15578794666667</v>
       </c>
       <c r="Q89">
-        <v>-11.02559338666667</v>
+        <v>-11.41578794666667</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2312834966450173</v>
+        <v>0.2467404546987688</v>
       </c>
       <c r="T89">
-        <v>3.518553390963579</v>
+        <v>3.811766173543877</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1071162257679233</v>
+        <v>0.1058989959296514</v>
       </c>
       <c r="W89">
-        <v>0.179291061865801</v>
+        <v>0.179535481617326</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5355811288396162</v>
+        <v>0.529494979648257</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1876000783870991</v>
+        <v>0.1891500783870991</v>
       </c>
       <c r="C90">
-        <v>-138.1975994374553</v>
+        <v>-141.2177949112691</v>
       </c>
       <c r="D90">
-        <v>61.95440056254468</v>
+        <v>61.3632050887309</v>
       </c>
       <c r="E90">
-        <v>82.852</v>
+        <v>85.28100000000001</v>
       </c>
       <c r="F90">
-        <v>213.752</v>
+        <v>216.181</v>
       </c>
       <c r="G90">
         <v>13.6</v>
@@ -8655,37 +8655,37 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M90">
-        <v>42.9214016</v>
+        <v>43.40914480000001</v>
       </c>
       <c r="N90">
-        <v>-20.19473493333334</v>
+        <v>-20.68247813333334</v>
       </c>
       <c r="O90">
-        <v>-4.038946986666668</v>
+        <v>-4.136495626666668</v>
       </c>
       <c r="P90">
-        <v>-16.15578794666667</v>
+        <v>-16.54598250666667</v>
       </c>
       <c r="Q90">
-        <v>-11.41578794666667</v>
+        <v>-11.80598250666667</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2467404546987688</v>
+        <v>0.2650077687622933</v>
       </c>
       <c r="T90">
-        <v>3.811766173543877</v>
+        <v>4.158290371138777</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1058989959296514</v>
+        <v>0.1047091195708913</v>
       </c>
       <c r="W90">
-        <v>0.179535481617326</v>
+        <v>0.179774408790165</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.529494979648257</v>
+        <v>0.5235455978544563</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1891500783870991</v>
+        <v>0.1907000783870992</v>
       </c>
       <c r="C91">
-        <v>-141.2177949112691</v>
+        <v>-144.2268141517297</v>
       </c>
       <c r="D91">
-        <v>61.3632050887309</v>
+        <v>60.78318584827029</v>
       </c>
       <c r="E91">
-        <v>85.28100000000001</v>
+        <v>87.71000000000001</v>
       </c>
       <c r="F91">
-        <v>216.181</v>
+        <v>218.61</v>
       </c>
       <c r="G91">
         <v>13.6</v>
@@ -8737,37 +8737,37 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M91">
-        <v>43.40914480000001</v>
+        <v>43.896888</v>
       </c>
       <c r="N91">
-        <v>-20.68247813333334</v>
+        <v>-21.17022133333334</v>
       </c>
       <c r="O91">
-        <v>-4.136495626666668</v>
+        <v>-4.234044266666667</v>
       </c>
       <c r="P91">
-        <v>-16.54598250666667</v>
+        <v>-16.93617706666667</v>
       </c>
       <c r="Q91">
-        <v>-11.80598250666667</v>
+        <v>-12.19617706666667</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2650077687622933</v>
+        <v>0.2869285456385225</v>
       </c>
       <c r="T91">
-        <v>4.158290371138777</v>
+        <v>4.574119408252654</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1047091195708913</v>
+        <v>0.1035456849089925</v>
       </c>
       <c r="W91">
-        <v>0.179774408790165</v>
+        <v>0.1800080264702743</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5235455978544563</v>
+        <v>0.5177284245449624</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1907000783870992</v>
+        <v>0.1922500783870991</v>
       </c>
       <c r="C92">
-        <v>-144.2268141517297</v>
+        <v>-147.224971112322</v>
       </c>
       <c r="D92">
-        <v>60.78318584827029</v>
+        <v>60.21402888767798</v>
       </c>
       <c r="E92">
-        <v>87.71000000000001</v>
+        <v>90.13900000000001</v>
       </c>
       <c r="F92">
-        <v>218.61</v>
+        <v>221.039</v>
       </c>
       <c r="G92">
         <v>13.6</v>
@@ -8819,37 +8819,37 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M92">
-        <v>43.896888</v>
+        <v>44.3846312</v>
       </c>
       <c r="N92">
-        <v>-21.17022133333334</v>
+        <v>-21.65796453333333</v>
       </c>
       <c r="O92">
-        <v>-4.234044266666667</v>
+        <v>-4.331592906666667</v>
       </c>
       <c r="P92">
-        <v>-16.93617706666667</v>
+        <v>-17.32637162666667</v>
       </c>
       <c r="Q92">
-        <v>-12.19617706666667</v>
+        <v>-12.58637162666667</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2869285456385225</v>
+        <v>0.3137206062650251</v>
       </c>
       <c r="T92">
-        <v>4.574119408252654</v>
+        <v>5.082354898058504</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1035456849089925</v>
+        <v>0.1024078202396629</v>
       </c>
       <c r="W92">
-        <v>0.1800080264702743</v>
+        <v>0.1802365096958757</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5177284245449624</v>
+        <v>0.5120391011983145</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1922500783870991</v>
+        <v>0.1938000783870991</v>
       </c>
       <c r="C93">
-        <v>-147.224971112322</v>
+        <v>-150.2125680965235</v>
       </c>
       <c r="D93">
-        <v>60.21402888767798</v>
+        <v>59.65543190347648</v>
       </c>
       <c r="E93">
-        <v>90.13900000000001</v>
+        <v>92.56800000000001</v>
       </c>
       <c r="F93">
-        <v>221.039</v>
+        <v>223.468</v>
       </c>
       <c r="G93">
         <v>13.6</v>
@@ -8901,37 +8901,37 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M93">
-        <v>44.3846312</v>
+        <v>44.87237440000001</v>
       </c>
       <c r="N93">
-        <v>-21.65796453333333</v>
+        <v>-22.14570773333334</v>
       </c>
       <c r="O93">
-        <v>-4.331592906666667</v>
+        <v>-4.429141546666668</v>
       </c>
       <c r="P93">
-        <v>-17.32637162666667</v>
+        <v>-17.71656618666667</v>
       </c>
       <c r="Q93">
-        <v>-12.58637162666667</v>
+        <v>-12.97656618666667</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3137206062650251</v>
+        <v>0.3472106820481533</v>
       </c>
       <c r="T93">
-        <v>5.082354898058504</v>
+        <v>5.717649260315819</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1024078202396629</v>
+        <v>0.101294691758797</v>
       </c>
       <c r="W93">
-        <v>0.1802365096958757</v>
+        <v>0.1804600258948336</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5120391011983145</v>
+        <v>0.506473458793985</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1938000783870991</v>
+        <v>0.1953500783870991</v>
       </c>
       <c r="C94">
-        <v>-150.2125680965235</v>
+        <v>-153.1898962932148</v>
       </c>
       <c r="D94">
-        <v>59.65543190347648</v>
+        <v>59.10710370678523</v>
       </c>
       <c r="E94">
-        <v>92.56800000000001</v>
+        <v>94.99700000000001</v>
       </c>
       <c r="F94">
-        <v>223.468</v>
+        <v>225.897</v>
       </c>
       <c r="G94">
         <v>13.6</v>
@@ -8983,37 +8983,37 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M94">
-        <v>44.87237440000001</v>
+        <v>45.3601176</v>
       </c>
       <c r="N94">
-        <v>-22.14570773333334</v>
+        <v>-22.63345093333334</v>
       </c>
       <c r="O94">
-        <v>-4.429141546666668</v>
+        <v>-4.526690186666667</v>
       </c>
       <c r="P94">
-        <v>-17.71656618666667</v>
+        <v>-18.10676074666667</v>
       </c>
       <c r="Q94">
-        <v>-12.97656618666667</v>
+        <v>-13.36676074666667</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3472106820481533</v>
+        <v>0.3902693509121753</v>
       </c>
       <c r="T94">
-        <v>5.717649260315819</v>
+        <v>6.534456297503795</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.101294691758797</v>
+        <v>0.1002055015248314</v>
       </c>
       <c r="W94">
-        <v>0.1804600258948336</v>
+        <v>0.1806787352938138</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.506473458793985</v>
+        <v>0.5010275076241572</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1953500783870991</v>
+        <v>0.2301678952354546</v>
       </c>
       <c r="C95">
-        <v>-153.1898962932148</v>
+        <v>-165.7342944510353</v>
       </c>
       <c r="D95">
-        <v>59.10710370678523</v>
+        <v>48.99170554896477</v>
       </c>
       <c r="E95">
-        <v>94.99700000000001</v>
+        <v>97.42600000000002</v>
       </c>
       <c r="F95">
-        <v>225.897</v>
+        <v>228.326</v>
       </c>
       <c r="G95">
         <v>13.6</v>
@@ -9065,45 +9065,45 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M95">
-        <v>45.3601176</v>
+        <v>53.83927080000001</v>
       </c>
       <c r="N95">
-        <v>-22.63345093333334</v>
+        <v>-31.11260413333334</v>
       </c>
       <c r="O95">
-        <v>-4.526690186666667</v>
+        <v>-6.222520826666669</v>
       </c>
       <c r="P95">
-        <v>-18.10676074666667</v>
+        <v>-24.89008330666667</v>
       </c>
       <c r="Q95">
-        <v>-13.36676074666667</v>
+        <v>-20.15008330666667</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3902693509121753</v>
+        <v>0.4538111902034608</v>
       </c>
       <c r="T95">
-        <v>6.534456297503795</v>
+        <v>7.739821508697216</v>
       </c>
       <c r="U95">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1002055015248314</v>
+        <v>0.08442412510039665</v>
       </c>
       <c r="W95">
-        <v>0.1806787352938138</v>
+        <v>0.2158927913013265</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y95">
-        <v>0.5010275076241572</v>
+        <v>0.4221206255019833</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2301678952354546</v>
+        <v>0.2320678952354545</v>
       </c>
       <c r="C96">
-        <v>-165.7342944510353</v>
+        <v>-168.6165894400711</v>
       </c>
       <c r="D96">
-        <v>48.99170554896477</v>
+        <v>48.53841055992889</v>
       </c>
       <c r="E96">
-        <v>97.42600000000002</v>
+        <v>99.85500000000002</v>
       </c>
       <c r="F96">
-        <v>228.326</v>
+        <v>230.755</v>
       </c>
       <c r="G96">
         <v>13.6</v>
@@ -9147,37 +9147,37 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M96">
-        <v>53.83927080000001</v>
+        <v>54.41202900000001</v>
       </c>
       <c r="N96">
-        <v>-31.11260413333334</v>
+        <v>-31.68536233333334</v>
       </c>
       <c r="O96">
-        <v>-6.222520826666669</v>
+        <v>-6.337072466666669</v>
       </c>
       <c r="P96">
-        <v>-24.89008330666667</v>
+        <v>-25.34828986666668</v>
       </c>
       <c r="Q96">
-        <v>-20.15008330666667</v>
+        <v>-20.60828986666667</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4538111902034608</v>
+        <v>0.5354134282441532</v>
       </c>
       <c r="T96">
-        <v>7.739821508697216</v>
+        <v>9.287785810436663</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.08442412510039665</v>
+        <v>0.08353545009933985</v>
       </c>
       <c r="W96">
-        <v>0.2158927913013265</v>
+        <v>0.2161023408665757</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4221206255019833</v>
+        <v>0.4176772504966992</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2320678952354545</v>
+        <v>0.2339678952354545</v>
       </c>
       <c r="C97">
-        <v>-168.6165894400711</v>
+        <v>-171.4905731197796</v>
       </c>
       <c r="D97">
-        <v>48.53841055992889</v>
+        <v>48.09342688022042</v>
       </c>
       <c r="E97">
-        <v>99.85500000000002</v>
+        <v>102.284</v>
       </c>
       <c r="F97">
-        <v>230.755</v>
+        <v>233.184</v>
       </c>
       <c r="G97">
         <v>13.6</v>
@@ -9229,37 +9229,37 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M97">
-        <v>54.41202900000001</v>
+        <v>54.98478720000001</v>
       </c>
       <c r="N97">
-        <v>-31.68536233333334</v>
+        <v>-32.25812053333334</v>
       </c>
       <c r="O97">
-        <v>-6.337072466666669</v>
+        <v>-6.451624106666668</v>
       </c>
       <c r="P97">
-        <v>-25.34828986666668</v>
+        <v>-25.80649642666667</v>
       </c>
       <c r="Q97">
-        <v>-20.60828986666667</v>
+        <v>-21.06649642666667</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5354134282441532</v>
+        <v>0.6578167853051918</v>
       </c>
       <c r="T97">
-        <v>9.287785810436663</v>
+        <v>11.60973226304584</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.08353545009933985</v>
+        <v>0.08266528916080507</v>
       </c>
       <c r="W97">
-        <v>0.2161023408665757</v>
+        <v>0.2163075248158822</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4176772504966992</v>
+        <v>0.4133264458040253</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2339678952354545</v>
+        <v>0.2358678952354545</v>
       </c>
       <c r="C98">
-        <v>-171.4905731197796</v>
+        <v>-174.3564719993927</v>
       </c>
       <c r="D98">
-        <v>48.09342688022042</v>
+        <v>47.65652800060725</v>
       </c>
       <c r="E98">
-        <v>102.284</v>
+        <v>104.713</v>
       </c>
       <c r="F98">
-        <v>233.184</v>
+        <v>235.613</v>
       </c>
       <c r="G98">
         <v>13.6</v>
@@ -9311,37 +9311,37 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M98">
-        <v>54.9847872</v>
+        <v>55.5575454</v>
       </c>
       <c r="N98">
-        <v>-32.25812053333333</v>
+        <v>-32.83087873333334</v>
       </c>
       <c r="O98">
-        <v>-6.451624106666667</v>
+        <v>-6.566175746666667</v>
       </c>
       <c r="P98">
-        <v>-25.80649642666667</v>
+        <v>-26.26470298666667</v>
       </c>
       <c r="Q98">
-        <v>-21.06649642666667</v>
+        <v>-21.52470298666667</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6578167853051902</v>
+        <v>0.8618223804069203</v>
       </c>
       <c r="T98">
-        <v>11.6097322630458</v>
+        <v>15.47964301739441</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.08266528916080507</v>
+        <v>0.08181306968492048</v>
       </c>
       <c r="W98">
-        <v>0.2163075248158822</v>
+        <v>0.2165084781682957</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4133264458040253</v>
+        <v>0.4090653484246024</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2358678952354545</v>
+        <v>0.2377678952354545</v>
       </c>
       <c r="C99">
-        <v>-174.3564719993927</v>
+        <v>-177.2145044314592</v>
       </c>
       <c r="D99">
-        <v>47.65652800060725</v>
+        <v>47.22749556854077</v>
       </c>
       <c r="E99">
-        <v>104.713</v>
+        <v>107.142</v>
       </c>
       <c r="F99">
-        <v>235.613</v>
+        <v>238.042</v>
       </c>
       <c r="G99">
         <v>13.6</v>
@@ -9393,37 +9393,37 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M99">
-        <v>55.5575454</v>
+        <v>56.1303036</v>
       </c>
       <c r="N99">
-        <v>-32.83087873333334</v>
+        <v>-33.40363693333334</v>
       </c>
       <c r="O99">
-        <v>-6.566175746666667</v>
+        <v>-6.680727386666668</v>
       </c>
       <c r="P99">
-        <v>-26.26470298666667</v>
+        <v>-26.72290954666667</v>
       </c>
       <c r="Q99">
-        <v>-21.52470298666667</v>
+        <v>-21.98290954666667</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8618223804069203</v>
+        <v>1.26983357061038</v>
       </c>
       <c r="T99">
-        <v>15.47964301739441</v>
+        <v>23.21946452609161</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.08181306968492048</v>
+        <v>0.08097824244323762</v>
       </c>
       <c r="W99">
-        <v>0.2165084781682957</v>
+        <v>0.2167053304318846</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4090653484246024</v>
+        <v>0.4048912122161881</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2377678952354545</v>
+        <v>0.2396678952354545</v>
       </c>
       <c r="C100">
-        <v>-177.2145044314592</v>
+        <v>-180.0648809757245</v>
       </c>
       <c r="D100">
-        <v>47.22749556854077</v>
+        <v>46.80611902427547</v>
       </c>
       <c r="E100">
-        <v>107.142</v>
+        <v>109.571</v>
       </c>
       <c r="F100">
-        <v>238.042</v>
+        <v>240.471</v>
       </c>
       <c r="G100">
         <v>13.6</v>
@@ -9475,37 +9475,37 @@
         <v>22.72666666666667</v>
       </c>
       <c r="M100">
-        <v>56.1303036</v>
+        <v>56.7030618</v>
       </c>
       <c r="N100">
-        <v>-33.40363693333334</v>
+        <v>-33.97639513333333</v>
       </c>
       <c r="O100">
-        <v>-6.680727386666668</v>
+        <v>-6.795279026666667</v>
       </c>
       <c r="P100">
-        <v>-26.72290954666667</v>
+        <v>-27.18111610666667</v>
       </c>
       <c r="Q100">
-        <v>-21.98290954666667</v>
+        <v>-22.44111610666667</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.26983357061038</v>
+        <v>2.493867141220761</v>
       </c>
       <c r="T100">
-        <v>23.21946452609161</v>
+        <v>46.43892905218321</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.08097824244323762</v>
+        <v>0.08016028039835643</v>
       </c>
       <c r="W100">
-        <v>0.2167053304318846</v>
+        <v>0.2168982058820676</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4048912122161881</v>
+        <v>0.4008014019917822</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2396678952354545</v>
-      </c>
-      <c r="C101">
-        <v>-180.0648809757245</v>
-      </c>
-      <c r="D101">
-        <v>46.80611902427547</v>
-      </c>
-      <c r="E101">
-        <v>109.571</v>
-      </c>
-      <c r="F101">
-        <v>240.471</v>
-      </c>
-      <c r="G101">
-        <v>13.6</v>
-      </c>
-      <c r="H101">
-        <v>112</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>27.46666666666667</v>
-      </c>
-      <c r="K101">
-        <v>4.74</v>
-      </c>
-      <c r="L101">
-        <v>22.72666666666667</v>
-      </c>
-      <c r="M101">
-        <v>56.7030618</v>
-      </c>
-      <c r="N101">
-        <v>-33.97639513333333</v>
-      </c>
-      <c r="O101">
-        <v>-6.795279026666667</v>
-      </c>
-      <c r="P101">
-        <v>-27.18111610666667</v>
-      </c>
-      <c r="Q101">
-        <v>-22.44111610666667</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.493867141220761</v>
-      </c>
-      <c r="T101">
-        <v>46.43892905218321</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.08016028039835643</v>
-      </c>
-      <c r="W101">
-        <v>0.2168982058820676</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4008014019917822</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
